--- a/data_raw/List_congreso.xlsx
+++ b/data_raw/List_congreso.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMONTOY\Desktop\proyectos_idic\Dashboard_Congresos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMONTOY\Desktop\proyectos_idic\Dashboard_Congresos\data_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D43239F-5D34-430B-AE52-0F381A590757}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C09D2DF-FF81-4B20-BBE1-1997AA4D0DD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11385" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="360">
   <si>
     <t>Evento</t>
   </si>
@@ -1441,6 +1441,60 @@
       </rPr>
       <t xml:space="preserve">
 </t>
+    </r>
+  </si>
+  <si>
+    <t>ECRM 2026</t>
+  </si>
+  <si>
+    <t>ECRM 2026 (European Conference on Research Methods in Business &amp; Management Studies)</t>
+  </si>
+  <si>
+    <t>Métodos de investigación cualitativa; Investigación basada en estudios de caso; Etnografía; Teoría fundamentada; Análisis narrativo y del discurso; Métodos de investigación cuantitativa; Técnicas estadísticas y análisis de datos; Diseño e implementación de encuestas; Diseños experimentales y cuasi-experimentales; Métodos mixtos de investigación; Integración de métodos cualitativos y cuantitativos; Técnicas de triangulación; Métodos de investigación innovadores y emergentes; Métodos de investigación digitales y en línea; Inteligencia artificial y machine learning en investigación; Métodos visuales; Epistemología y ontología en investigación; Desarrollo de teorías y marcos conceptuales; Ética en la investigación; Integridad y ética científica; Desafíos éticos en investigación digital; Investigación aplicada en negocios; Investigación acción; Métodos participativos; Consultoría e investigación empresarial; Investigación en economías emergentes</t>
+  </si>
+  <si>
+    <t>Cape Peninsula University of Technology (CPUT)</t>
+  </si>
+  <si>
+    <t>Ciudad del Cabo</t>
+  </si>
+  <si>
+    <t>Sudáfrica</t>
+  </si>
+  <si>
+    <t>https://www.academic-conferences.org/conferences/ecrm/</t>
+  </si>
+  <si>
+    <t>Educación, desarrollo cognitivo y socioafectivo; Inteligencia de negocios; Internet de las cosas (IoT); Machine learning y deep learning; Procesamiento de lenguaje natural</t>
+  </si>
+  <si>
+    <t>El sitio web indica a los miembros del Comité de la conferencia ECRM</t>
+  </si>
+  <si>
+    <t>Temario: 
+Qualitative Research Methods
+Quantitative Research Methods
+Mixed and Innovative Research Methodologies
+Teaching and Learning Research Methods
+Ethics and Best Practices in Research</t>
+  </si>
+  <si>
+    <t>El sitio web indica que todos los artículos son revisados ​​por pares a doble ciego por miembros del comité de la conferencia</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El sitio web indica que las actas estarán disponibles en el siguiente enlace: https://papers.academic-conferences.org/index.php/ecmlg
+Las publicaciones del 2025 aun no están visibles en Scopus porque el evento se desarrolló en noviembre 2025. Asimismo, se indica que los trabajos presentados en la conferencia también se considerarán para su posterior poblicación en la revista </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Electronic Journal of Business Research Methods </t>
     </r>
   </si>
 </sst>
@@ -1552,7 +1606,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1591,6 +1645,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF6B26B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9900"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1837,7 +1897,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2070,6 +2130,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2359,7 +2428,7 @@
     <col min="16382" max="16384" width="11.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="14" customFormat="1" ht="75.75" thickBot="1">
+    <row r="1" spans="1:24" s="14" customFormat="1" ht="60.75" thickBot="1">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -3907,20 +3976,79 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15.75" thickBot="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="9"/>
+    <row r="22" spans="1:24" ht="117.75" customHeight="1" thickBot="1">
+      <c r="A22" s="84" t="s">
+        <v>348</v>
+      </c>
+      <c r="B22" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="C22" s="62" t="s">
+        <v>350</v>
+      </c>
+      <c r="D22" s="62">
+        <v>2026</v>
+      </c>
+      <c r="E22" s="63">
+        <v>46181</v>
+      </c>
+      <c r="F22" s="63">
+        <v>46211</v>
+      </c>
+      <c r="G22" s="64">
+        <v>46145</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>351</v>
+      </c>
+      <c r="I22" s="62" t="s">
+        <v>352</v>
+      </c>
+      <c r="J22" s="62" t="s">
+        <v>353</v>
+      </c>
+      <c r="K22" s="62" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="62" t="s">
+        <v>230</v>
+      </c>
+      <c r="M22" s="65" t="s">
+        <v>354</v>
+      </c>
+      <c r="N22" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="O22" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="P22" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q22" s="85" t="s">
+        <v>343</v>
+      </c>
+      <c r="R22" s="66" t="s">
+        <v>356</v>
+      </c>
+      <c r="S22" s="86" t="s">
+        <v>357</v>
+      </c>
+      <c r="T22" s="86" t="s">
+        <v>358</v>
+      </c>
+      <c r="U22" s="66" t="s">
+        <v>359</v>
+      </c>
+      <c r="V22" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="W22" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="X22" s="66" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="23" spans="1:24" ht="15.75" thickBot="1">
       <c r="A23" s="5"/>
@@ -3982,8 +4110,9 @@
     <hyperlink ref="M19" r:id="rId11" xr:uid="{495DF37F-611C-4C96-9B59-B91FD1969EB1}"/>
     <hyperlink ref="M20" r:id="rId12" xr:uid="{8764E6FA-24BB-4CD3-B7F0-A477686AF5B7}"/>
     <hyperlink ref="M21" r:id="rId13" xr:uid="{9E69CB45-2D00-482D-B3EC-C054EF664AFF}"/>
+    <hyperlink ref="M22" r:id="rId14" xr:uid="{5CCA6143-A9EC-4CB6-B3D2-4F8671964932}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId15"/>
 </worksheet>
 </file>
--- a/data_raw/List_congreso.xlsx
+++ b/data_raw/List_congreso.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CAMONTOY\Desktop\proyectos_idic\Dashboard_Congresos\data_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C09D2DF-FF81-4B20-BBE1-1997AA4D0DD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF172751-C29D-4E67-BA33-7F37AD512B2B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11385" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="389">
   <si>
     <t>Evento</t>
   </si>
@@ -394,9 +394,6 @@
     <t>San jose</t>
   </si>
   <si>
-    <t>CIDIP/ICPME 2026</t>
-  </si>
-  <si>
     <t>30th International Congress on Project Management and Engineering</t>
   </si>
   <si>
@@ -655,9 +652,6 @@
     <t>29/3/2026</t>
   </si>
   <si>
-    <t>IEEE LAMC 2026</t>
-  </si>
-  <si>
     <t>6th IEEE MTT-S Latin America Microwave Conference</t>
   </si>
   <si>
@@ -698,9 +692,6 @@
   </si>
   <si>
     <t>https://www.acit.tech/</t>
-  </si>
-  <si>
-    <t>ECMLG 2026</t>
   </si>
   <si>
     <t>22nd European Conference on Management, Leadership and Governance)</t>
@@ -1444,9 +1435,6 @@
     </r>
   </si>
   <si>
-    <t>ECRM 2026</t>
-  </si>
-  <si>
     <t>ECRM 2026 (European Conference on Research Methods in Business &amp; Management Studies)</t>
   </si>
   <si>
@@ -1496,6 +1484,169 @@
       </rPr>
       <t xml:space="preserve">Electronic Journal of Business Research Methods </t>
     </r>
+  </si>
+  <si>
+    <t>17th APCA International Conference on Automatic Control and Soft Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistemas de control; Control adaptativo; Control aeroespacial; Educación en control; Sensores y actuadores; Teoría de control; Arquitecturas de control; Sistemas de eventos discretos; Control distribuido; Estimación e identificación de sistemas; Detección de fallas; Diagnóstico de fallas; Control tolerante a fallas; Sistemas difusos; Sistemas neuro-difusos; Control con humano en el bucle; Sistemas híbridos; Control basado en inteligencia artificial; Control lineal; Control no lineal; Modelado y simulación; Sistemas de control en red; Control óptimo; Control robusto; Control estocástico; Optimización; Laboratorios remotos y virtuales; Automatización industrial; Sistemas automatizados; Robótica; Robots inteligentes; Sistemas ciberfísicos; Soft computing aplicado al control; Soft computing en robótica; Soft computing en automatización; Inteligencia computacional en control
+</t>
+  </si>
+  <si>
+    <t>Universidad de Coimbra, Portugal</t>
+  </si>
+  <si>
+    <t>Coimbra</t>
+  </si>
+  <si>
+    <t>controlo2026.apca.pt</t>
+  </si>
+  <si>
+    <t>12th ICACIT Symposium Advancing Quality, Artificial Intelligence, and Applied Innovation in Engineering and Computing Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acreditación en ingeniería y computación; Educación basada en resultados; Sistemas de mejora continua; Analítica de calidad educativa; Evaluación auténtica; Evaluación de programas académicos; Efectividad institucional; Integridad académica digital; Calidad en educación híbrida y virtual; Métricas de diversidad e inclusión; Inteligencia Artificial en educación; Inteligencia Artificial generativa en educación; Laboratorios virtuales y remotos; Entornos inmersivos de aprendizaje; Gemelos digitales; Sistemas ciberfísicos en educación; Ética de la IA en educación; Aprendizaje basado en proyectos; Aprendizaje basado en retos; Desarrollo de habilidades profesionales; Liderazgo y ética; Inclusión y diversidad en educación; Cambio climático; Ingeniería sostenible; Colaboración universidad-industria-gobierno; Innovación social; Emprendimiento tecnológico; Ética en ingeniería; Políticas públicas en ingeniería; Ingeniería de software aplicada; Desarrollo de prototipos; Pruebas de concepto; Validación tecnológica; Proyectos de tesis aplicados; Transferencia tecnológica
+</t>
+  </si>
+  <si>
+    <t>21/10/2026</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>30/06/2026</t>
+  </si>
+  <si>
+    <t>Pontificia Universidad Católica de Chile (UC) - Santiago, Chile</t>
+  </si>
+  <si>
+    <t>Híbrido</t>
+  </si>
+  <si>
+    <t>icacit.org.pe/symposium</t>
+  </si>
+  <si>
+    <t>Universidad de Coímbra</t>
+  </si>
+  <si>
+    <t>El sitio web cuenta con información referente a los siguientes comités: Comité Directivo, Comité Organizador, Comité de Programa</t>
+  </si>
+  <si>
+    <t>Temario:
+1. Sistemas de control
+Control adaptativo 
+Control aeronáutico y aeroespacial 
+Educación de control 
+Tecnología de control, sensores y actuadores 
+Teoría, arquitecturas y aplicaciones del control 
+Sistemas de eventos discretos 
+Control distribuido 
+Estimación e identificación 
+Detección de fallos, diagnóstico y control tolerante a fallos 
+Sistemas y control difusos y neurodifusos 
+Control con intervención humana 
+Sistemas híbridos 
+Control inteligente basado en IA 
+Control lineal y no lineal 
+Modelado y simulación 
+Sistemas de control en red 
+Control óptimo, robusto y estocástico 
+Enfoques de optimización 
+Laboratorios remotos y virtuales
+2. Automatización y Robótica
+Vehículos guiados automáticamente 
+Agentes autónomos 
+Sistemas ciberfísicos 
+Sistemas embebidos 
+Modelado y automatización de fábricas 
+Grafcet y redes de Petri 
+Interacción entre agentes y humanos 
+Interfaces hombre-máquina 
+Redes industriales y automatización 
+Automatización industrial 
+Instrumentación 
+Internet de las cosas e Industria 4.0 
+Sistemas de fabricación 
+Sistemas mecatrónicos 
+Robots móviles 
+Modelado de sistemas complejos 
+Percepción y Conciencia 
+Automatización de procesos 
+Sistemas en tiempo real 
+Robótica 
+Visión, reconocimiento y reconstrucción
+3. Computación blanda con aplicación al control, la automatización o la robótica
+Programación adaptativa y dinámica 
+Inteligencia artificial y reconocimiento de patrones 
+Nube, niebla y macrodatos 
+Sistemas artificiales cognitivos 
+Inteligencia computacional 
+Minería de datos y recuperación de información 
+Reducción e interpretación de datos 
+Evolución de los sistemas de IA 
+Computación independiente y cognitiva 
+Agentes inteligentes y conocimiento del contexto 
+Adquisición y representación del conocimiento 
+Aprendizaje automático 
+Sistemas de toma de decisiones inteligentes de percepción 
+Aprendizaje por refuerzo y aprendizaje profundo</t>
+  </si>
+  <si>
+    <t>El sitio web indica que las actas se publicarán en IEEE Explore. Todos los artículos revisados ​​por pares, aceptados y presentados se enviarán para su publicación en la biblioteca digital IEEE Xplore.</t>
+  </si>
+  <si>
+    <t>El sitio web indica que las actas se enviarán al Thomson Reuters Conference Proceedings Citation Index (ISI), INSPEC y Scopus para su indexación.</t>
+  </si>
+  <si>
+    <t>ICACIT (Instituto de Calidad y Acreditación de Programas de Computación, Ingeniería y Tecnología)</t>
+  </si>
+  <si>
+    <t>El sitio web indica a los miembros de su Comité Organizador, y Comité Directivo</t>
+  </si>
+  <si>
+    <t>Temario:
+Garantía de calidad, acreditación y educación basada en resultados en ingeniería o informática
+Transformación digital, inteligencia artificial y tecnologías emergentes en la formación en ingeniería
+Innovación curricular, estrategias pedagógicas y desarrollo estudiantil
+Sostenibilidad, impacto social e ingeniería o informática global
+Ingeniería aplicada, informática y proyectos vinculados a la industria o a la comunidad</t>
+  </si>
+  <si>
+    <t>El sitio web indica que todas las propuestas se someten a una revisión por pares a doble ciego realizada por revisores expertos</t>
+  </si>
+  <si>
+    <t>El sitio web indica que todos los artículos en inglés aceptados y presentados oralmente en el Simposio ICACIT 2026 se incluirán en las actas de la conferencia y se enviarán para su publicación a IEEE Xplore®. El contenido de IEEE Xplore® se pone a disposición de sus socios de resumen e indexación, Scopus, para su posible inclusión en sus respectivas bases de datos.</t>
+  </si>
+  <si>
+    <t>Ciudades inteligentes y sostenibles; Experiencia digital humana; Inteligencia artificial y computación avanzada; Transformación digital</t>
+  </si>
+  <si>
+    <t>Diseño de interfaces adaptativas; Gestión inteligente de recursos; Internet de las cosas (IoT); Machine learning y deep learning; Sistemas autónomos y robótica</t>
+  </si>
+  <si>
+    <t>Bienestar y desarrollo humano; Gestión del conocimiento; Inteligencia artificial y computación avanzada; Transformación digital; Ética, gobernanza y responsabilidad social</t>
+  </si>
+  <si>
+    <t>Educación, desarrollo cognitivo y socioafectivo; Inteligencia de negocios; Internet de las cosas (IoT); Machine learning y deep learning; Ética y gobernanza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICACIT Symposium </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROLO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECRM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECMLG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IEEE LAMC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDIP/ICPME </t>
   </si>
 </sst>
 </file>
@@ -1606,7 +1757,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1651,6 +1802,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF9900"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9CB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1897,7 +2054,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1905,9 +2062,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2140,6 +2294,18 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2405,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:TZ25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="27" style="1" customWidth="1"/>
@@ -2428,1672 +2594,3356 @@
     <col min="16382" max="16384" width="11.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="14" customFormat="1" ht="60.75" thickBot="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:546" s="13" customFormat="1" ht="60.75" thickBot="1">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="N1" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="O1" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="P1" s="26" t="s">
+      <c r="P1" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="79" t="s">
+      <c r="Q1" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="R1" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="S1" s="78" t="s">
+        <v>237</v>
+      </c>
+      <c r="T1" s="78" t="s">
         <v>238</v>
       </c>
-      <c r="R1" s="79" t="s">
+      <c r="U1" s="78" t="s">
         <v>239</v>
       </c>
-      <c r="S1" s="79" t="s">
+      <c r="V1" s="78" t="s">
         <v>240</v>
       </c>
-      <c r="T1" s="79" t="s">
+      <c r="W1" s="78" t="s">
         <v>241</v>
       </c>
-      <c r="U1" s="79" t="s">
+      <c r="X1" s="78" t="s">
         <v>242</v>
       </c>
-      <c r="V1" s="79" t="s">
+    </row>
+    <row r="2" spans="1:546" s="10" customFormat="1" ht="109.5" customHeight="1" thickBot="1">
+      <c r="A2" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="15">
+        <v>2026</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="M2" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="O2" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="P2" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q2" s="79" t="s">
         <v>243</v>
       </c>
-      <c r="W1" s="79" t="s">
+      <c r="R2" s="80"/>
+      <c r="S2" s="68" t="s">
         <v>244</v>
       </c>
-      <c r="X1" s="79" t="s">
+      <c r="T2" s="68" t="s">
         <v>245</v>
       </c>
+      <c r="U2" s="68" t="s">
+        <v>246</v>
+      </c>
+      <c r="V2" s="68" t="s">
+        <v>247</v>
+      </c>
+      <c r="W2" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="X2" s="68" t="s">
+        <v>249</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" s="11" customFormat="1" ht="109.5" customHeight="1" thickBot="1">
-      <c r="A2" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="16">
+    <row r="3" spans="1:546" s="10" customFormat="1" ht="94.5" customHeight="1" thickBot="1">
+      <c r="A3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="15">
         <v>2026</v>
       </c>
-      <c r="E2" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="16" t="s">
+      <c r="E3" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="P3" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q3" s="79" t="s">
+        <v>250</v>
+      </c>
+      <c r="R3" s="80"/>
+      <c r="S3" s="68" t="s">
+        <v>251</v>
+      </c>
+      <c r="T3" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="U3" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="V3" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W3" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="X3" s="68" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:546" s="10" customFormat="1" ht="120" customHeight="1" thickBot="1">
+      <c r="A4" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="15">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q4" s="79" t="s">
+        <v>254</v>
+      </c>
+      <c r="R4" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="S4" s="68" t="s">
+        <v>256</v>
+      </c>
+      <c r="T4" s="68" t="s">
+        <v>257</v>
+      </c>
+      <c r="U4" s="68" t="s">
+        <v>258</v>
+      </c>
+      <c r="V4" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W4" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="X4" s="68" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:546" s="10" customFormat="1" ht="127.5" customHeight="1" thickBot="1">
+      <c r="A5" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="17">
+        <v>2026</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="O5" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="P5" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q5" s="79" t="s">
+        <v>259</v>
+      </c>
+      <c r="R5" s="68" t="s">
+        <v>260</v>
+      </c>
+      <c r="S5" s="68" t="s">
+        <v>261</v>
+      </c>
+      <c r="T5" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="U5" s="68" t="s">
+        <v>262</v>
+      </c>
+      <c r="V5" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W5" s="80"/>
+      <c r="X5" s="68" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:546" s="10" customFormat="1" ht="120" customHeight="1" thickBot="1">
+      <c r="A6" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="17">
+        <v>2026</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="O6" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="P6" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q6" s="79" t="s">
+        <v>263</v>
+      </c>
+      <c r="R6" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="S6" s="68" t="s">
+        <v>265</v>
+      </c>
+      <c r="T6" s="68" t="s">
+        <v>266</v>
+      </c>
+      <c r="U6" s="68" t="s">
+        <v>267</v>
+      </c>
+      <c r="V6" s="67" t="s">
+        <v>252</v>
+      </c>
+      <c r="W6" s="67" t="s">
+        <v>268</v>
+      </c>
+      <c r="X6" s="67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:546" s="10" customFormat="1" ht="114" customHeight="1" thickBot="1">
+      <c r="A7" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="17">
+        <v>2026</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="M7" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="O7" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="P7" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q7" s="79" t="s">
+        <v>269</v>
+      </c>
+      <c r="R7" s="68" t="s">
+        <v>270</v>
+      </c>
+      <c r="S7" s="68" t="s">
+        <v>271</v>
+      </c>
+      <c r="T7" s="68" t="s">
+        <v>272</v>
+      </c>
+      <c r="U7" s="68" t="s">
+        <v>273</v>
+      </c>
+      <c r="V7" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W7" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="X7" s="68" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:546" s="10" customFormat="1" ht="132" customHeight="1" thickBot="1">
+      <c r="A8" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="20">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="O8" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="P8" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q8" s="79" t="s">
+        <v>274</v>
+      </c>
+      <c r="R8" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="S8" s="68" t="s">
+        <v>276</v>
+      </c>
+      <c r="T8" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="U8" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="V8" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W8" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="X8" s="67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:546" s="14" customFormat="1" ht="105.75" customHeight="1" thickBot="1">
+      <c r="A9" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="20">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="O9" s="35" t="s">
+        <v>116</v>
+      </c>
+      <c r="P9" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q9" s="79" t="s">
+        <v>279</v>
+      </c>
+      <c r="R9" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="S9" s="68" t="s">
+        <v>280</v>
+      </c>
+      <c r="T9" s="68" t="s">
+        <v>281</v>
+      </c>
+      <c r="U9" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="V9" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W9" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="X9" s="67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:546" ht="95.25" customHeight="1" thickBot="1">
+      <c r="A10" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="20">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="24">
+        <v>46026</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="N10" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="O10" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="P10" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q10" s="79" t="s">
+        <v>283</v>
+      </c>
+      <c r="R10" s="68" t="s">
+        <v>275</v>
+      </c>
+      <c r="S10" s="68" t="s">
+        <v>284</v>
+      </c>
+      <c r="T10" s="68" t="s">
+        <v>285</v>
+      </c>
+      <c r="U10" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="V10" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W10" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="X10" s="67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:546" ht="108" customHeight="1" thickBot="1">
+      <c r="A11" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="28">
+        <v>2026</v>
+      </c>
+      <c r="E11" s="41">
+        <v>46331</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="29">
+        <v>46175</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="M11" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="N11" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="O11" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="P11" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q11" s="79" t="s">
+        <v>287</v>
+      </c>
+      <c r="R11" s="68" t="s">
+        <v>288</v>
+      </c>
+      <c r="S11" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="T11" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="U11" s="68" t="s">
+        <v>291</v>
+      </c>
+      <c r="V11" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W11" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="X11" s="67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:546" ht="156" customHeight="1" thickBot="1">
+      <c r="A12" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="32">
+        <v>2026</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" s="33">
+        <v>46240</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="M12" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="N12" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="O12" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="P12" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q12" s="79" t="s">
+        <v>293</v>
+      </c>
+      <c r="R12" s="68" t="s">
+        <v>294</v>
+      </c>
+      <c r="S12" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="T12" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="U12" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="V12" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W12" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="X12" s="67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:546" ht="159.75" customHeight="1" thickBot="1">
+      <c r="A13" s="31" t="s">
+        <v>388</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="32">
+        <v>2026</v>
+      </c>
+      <c r="E13" s="33">
+        <v>46210</v>
+      </c>
+      <c r="F13" s="33">
+        <v>46272</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="N13" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="O13" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="P13" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q13" s="79" t="s">
+        <v>298</v>
+      </c>
+      <c r="R13" s="68" t="s">
+        <v>299</v>
+      </c>
+      <c r="S13" s="68" t="s">
+        <v>300</v>
+      </c>
+      <c r="T13" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="U13" s="68" t="s">
+        <v>302</v>
+      </c>
+      <c r="V13" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W13" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="X13" s="67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="14" spans="1:546" ht="135.75" customHeight="1" thickBot="1">
+      <c r="A14" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="32">
+        <v>2026</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F14" s="33">
+        <v>46063</v>
+      </c>
+      <c r="G14" s="33">
+        <v>46030</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="J14" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="L14" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="N14" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="O14" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="P14" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q14" s="79" t="s">
+        <v>304</v>
+      </c>
+      <c r="R14" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="S14" s="68" t="s">
+        <v>306</v>
+      </c>
+      <c r="T14" s="68" t="s">
+        <v>307</v>
+      </c>
+      <c r="U14" s="68" t="s">
+        <v>308</v>
+      </c>
+      <c r="V14" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W14" s="68" t="s">
+        <v>248</v>
+      </c>
+      <c r="X14" s="68" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="1:546" ht="150.75" customHeight="1" thickBot="1">
+      <c r="A15" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="42">
+        <v>2026</v>
+      </c>
+      <c r="E15" s="44">
+        <v>46092</v>
+      </c>
+      <c r="F15" s="44">
+        <v>46153</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="I15" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="J15" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="M15" s="45" t="s">
+        <v>139</v>
+      </c>
+      <c r="N15" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="O15" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="P15" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q15" s="79" t="s">
+        <v>309</v>
+      </c>
+      <c r="R15" s="68" t="s">
+        <v>310</v>
+      </c>
+      <c r="S15" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="T15" s="68" t="s">
+        <v>312</v>
+      </c>
+      <c r="U15" s="68" t="s">
+        <v>313</v>
+      </c>
+      <c r="V15" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W15" s="68" t="s">
+        <v>314</v>
+      </c>
+      <c r="X15" s="68" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:546" s="47" customFormat="1" ht="87" customHeight="1" thickBot="1">
+      <c r="A16" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="50">
+        <v>2026</v>
+      </c>
+      <c r="E16" s="51">
+        <v>46090</v>
+      </c>
+      <c r="F16" s="51">
+        <v>46121</v>
+      </c>
+      <c r="G16" s="51">
+        <v>46115</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="I16" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="J16" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="M16" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="N16" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="O16" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="P16" s="58" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q16" s="79" t="s">
+        <v>315</v>
+      </c>
+      <c r="R16" s="68" t="s">
+        <v>316</v>
+      </c>
+      <c r="S16" s="68" t="s">
+        <v>317</v>
+      </c>
+      <c r="T16" s="67" t="s">
+        <v>318</v>
+      </c>
+      <c r="U16" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="V16" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W16" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="X16" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+      <c r="AI16" s="1"/>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1"/>
+      <c r="AL16" s="1"/>
+      <c r="AM16" s="1"/>
+      <c r="AN16" s="1"/>
+      <c r="AO16" s="1"/>
+      <c r="AP16" s="1"/>
+      <c r="AQ16" s="1"/>
+      <c r="AR16" s="1"/>
+      <c r="AS16" s="1"/>
+      <c r="AT16" s="1"/>
+      <c r="AU16" s="1"/>
+      <c r="AV16" s="1"/>
+      <c r="AW16" s="1"/>
+      <c r="AX16" s="1"/>
+      <c r="AY16" s="1"/>
+      <c r="AZ16" s="1"/>
+      <c r="BA16" s="1"/>
+      <c r="BB16" s="1"/>
+      <c r="BC16" s="1"/>
+      <c r="BD16" s="1"/>
+      <c r="BE16" s="1"/>
+      <c r="BF16" s="1"/>
+      <c r="BG16" s="1"/>
+      <c r="BH16" s="1"/>
+      <c r="BI16" s="1"/>
+      <c r="BJ16" s="1"/>
+      <c r="BK16" s="1"/>
+      <c r="BL16" s="1"/>
+      <c r="BM16" s="1"/>
+      <c r="BN16" s="1"/>
+      <c r="BO16" s="1"/>
+      <c r="BP16" s="1"/>
+      <c r="BQ16" s="1"/>
+      <c r="BR16" s="1"/>
+      <c r="BS16" s="1"/>
+      <c r="BT16" s="1"/>
+      <c r="BU16" s="1"/>
+      <c r="BV16" s="1"/>
+      <c r="BW16" s="1"/>
+      <c r="BX16" s="1"/>
+      <c r="BY16" s="1"/>
+      <c r="BZ16" s="1"/>
+      <c r="CA16" s="1"/>
+      <c r="CB16" s="1"/>
+      <c r="CC16" s="1"/>
+      <c r="CD16" s="1"/>
+      <c r="CE16" s="1"/>
+      <c r="CF16" s="1"/>
+      <c r="CG16" s="1"/>
+      <c r="CH16" s="1"/>
+      <c r="CI16" s="1"/>
+      <c r="CJ16" s="1"/>
+      <c r="CK16" s="1"/>
+      <c r="CL16" s="1"/>
+      <c r="CM16" s="1"/>
+      <c r="CN16" s="1"/>
+      <c r="CO16" s="1"/>
+      <c r="CP16" s="1"/>
+      <c r="CQ16" s="1"/>
+      <c r="CR16" s="1"/>
+      <c r="CS16" s="1"/>
+      <c r="CT16" s="1"/>
+      <c r="CU16" s="1"/>
+      <c r="CV16" s="1"/>
+      <c r="CW16" s="1"/>
+      <c r="CX16" s="1"/>
+      <c r="CY16" s="1"/>
+      <c r="CZ16" s="1"/>
+      <c r="DA16" s="1"/>
+      <c r="DB16" s="1"/>
+      <c r="DC16" s="1"/>
+      <c r="DD16" s="1"/>
+      <c r="DE16" s="1"/>
+      <c r="DF16" s="1"/>
+      <c r="DG16" s="1"/>
+      <c r="DH16" s="1"/>
+      <c r="DI16" s="1"/>
+      <c r="DJ16" s="1"/>
+      <c r="DK16" s="1"/>
+      <c r="DL16" s="1"/>
+      <c r="DM16" s="1"/>
+      <c r="DN16" s="1"/>
+      <c r="DO16" s="1"/>
+      <c r="DP16" s="1"/>
+      <c r="DQ16" s="1"/>
+      <c r="DR16" s="1"/>
+      <c r="DS16" s="1"/>
+      <c r="DT16" s="1"/>
+      <c r="DU16" s="1"/>
+      <c r="DV16" s="1"/>
+      <c r="DW16" s="1"/>
+      <c r="DX16" s="1"/>
+      <c r="DY16" s="1"/>
+      <c r="DZ16" s="1"/>
+      <c r="EA16" s="1"/>
+      <c r="EB16" s="1"/>
+      <c r="EC16" s="1"/>
+      <c r="ED16" s="1"/>
+      <c r="EE16" s="1"/>
+      <c r="EF16" s="1"/>
+      <c r="EG16" s="1"/>
+      <c r="EH16" s="1"/>
+      <c r="EI16" s="1"/>
+      <c r="EJ16" s="1"/>
+      <c r="EK16" s="1"/>
+      <c r="EL16" s="1"/>
+      <c r="EM16" s="1"/>
+      <c r="EN16" s="1"/>
+      <c r="EO16" s="1"/>
+      <c r="EP16" s="1"/>
+      <c r="EQ16" s="1"/>
+      <c r="ER16" s="1"/>
+      <c r="ES16" s="1"/>
+      <c r="ET16" s="1"/>
+      <c r="EU16" s="1"/>
+      <c r="EV16" s="1"/>
+      <c r="EW16" s="1"/>
+      <c r="EX16" s="1"/>
+      <c r="EY16" s="1"/>
+      <c r="EZ16" s="1"/>
+      <c r="FA16" s="1"/>
+      <c r="FB16" s="1"/>
+      <c r="FC16" s="1"/>
+      <c r="FD16" s="1"/>
+      <c r="FE16" s="1"/>
+      <c r="FF16" s="1"/>
+      <c r="FG16" s="1"/>
+      <c r="FH16" s="1"/>
+      <c r="FI16" s="1"/>
+      <c r="FJ16" s="1"/>
+      <c r="FK16" s="1"/>
+      <c r="FL16" s="1"/>
+      <c r="FM16" s="1"/>
+      <c r="FN16" s="1"/>
+      <c r="FO16" s="1"/>
+      <c r="FP16" s="1"/>
+      <c r="FQ16" s="1"/>
+      <c r="FR16" s="1"/>
+      <c r="FS16" s="1"/>
+      <c r="FT16" s="1"/>
+      <c r="FU16" s="1"/>
+      <c r="FV16" s="1"/>
+      <c r="FW16" s="1"/>
+      <c r="FX16" s="1"/>
+      <c r="FY16" s="1"/>
+      <c r="FZ16" s="1"/>
+      <c r="GA16" s="1"/>
+      <c r="GB16" s="1"/>
+      <c r="GC16" s="1"/>
+      <c r="GD16" s="1"/>
+      <c r="GE16" s="1"/>
+      <c r="GF16" s="1"/>
+      <c r="GG16" s="1"/>
+      <c r="GH16" s="1"/>
+      <c r="GI16" s="1"/>
+      <c r="GJ16" s="1"/>
+      <c r="GK16" s="1"/>
+      <c r="GL16" s="1"/>
+      <c r="GM16" s="1"/>
+      <c r="GN16" s="1"/>
+      <c r="GO16" s="1"/>
+      <c r="GP16" s="1"/>
+      <c r="GQ16" s="1"/>
+      <c r="GR16" s="1"/>
+      <c r="GS16" s="1"/>
+      <c r="GT16" s="1"/>
+      <c r="GU16" s="1"/>
+      <c r="GV16" s="1"/>
+      <c r="GW16" s="1"/>
+      <c r="GX16" s="1"/>
+      <c r="GY16" s="1"/>
+      <c r="GZ16" s="1"/>
+      <c r="HA16" s="1"/>
+      <c r="HB16" s="1"/>
+      <c r="HC16" s="1"/>
+      <c r="HD16" s="1"/>
+      <c r="HE16" s="1"/>
+      <c r="HF16" s="1"/>
+      <c r="HG16" s="1"/>
+      <c r="HH16" s="1"/>
+      <c r="HI16" s="1"/>
+      <c r="HJ16" s="1"/>
+      <c r="HK16" s="1"/>
+      <c r="HL16" s="1"/>
+      <c r="HM16" s="1"/>
+      <c r="HN16" s="1"/>
+      <c r="HO16" s="1"/>
+      <c r="HP16" s="1"/>
+      <c r="HQ16" s="1"/>
+      <c r="HR16" s="1"/>
+      <c r="HS16" s="1"/>
+      <c r="HT16" s="1"/>
+      <c r="HU16" s="1"/>
+      <c r="HV16" s="1"/>
+      <c r="HW16" s="1"/>
+      <c r="HX16" s="1"/>
+      <c r="HY16" s="1"/>
+      <c r="HZ16" s="1"/>
+      <c r="IA16" s="1"/>
+      <c r="IB16" s="1"/>
+      <c r="IC16" s="1"/>
+      <c r="ID16" s="1"/>
+      <c r="IE16" s="1"/>
+      <c r="IF16" s="1"/>
+      <c r="IG16" s="1"/>
+      <c r="IH16" s="1"/>
+      <c r="II16" s="1"/>
+      <c r="IJ16" s="1"/>
+      <c r="IK16" s="1"/>
+      <c r="IL16" s="1"/>
+      <c r="IM16" s="1"/>
+      <c r="IN16" s="1"/>
+      <c r="IO16" s="1"/>
+      <c r="IP16" s="1"/>
+      <c r="IQ16" s="1"/>
+      <c r="IR16" s="1"/>
+      <c r="IS16" s="1"/>
+      <c r="IT16" s="1"/>
+      <c r="IU16" s="1"/>
+      <c r="IV16" s="1"/>
+      <c r="IW16" s="1"/>
+      <c r="IX16" s="1"/>
+      <c r="IY16" s="1"/>
+      <c r="IZ16" s="1"/>
+      <c r="JA16" s="1"/>
+      <c r="JB16" s="1"/>
+      <c r="JC16" s="1"/>
+      <c r="JD16" s="1"/>
+      <c r="JE16" s="1"/>
+      <c r="JF16" s="1"/>
+      <c r="JG16" s="1"/>
+      <c r="JH16" s="1"/>
+      <c r="JI16" s="1"/>
+      <c r="JJ16" s="1"/>
+      <c r="JK16" s="1"/>
+      <c r="JL16" s="1"/>
+      <c r="JM16" s="1"/>
+      <c r="JN16" s="1"/>
+      <c r="JO16" s="1"/>
+      <c r="JP16" s="1"/>
+      <c r="JQ16" s="1"/>
+      <c r="JR16" s="1"/>
+      <c r="JS16" s="1"/>
+      <c r="JT16" s="1"/>
+      <c r="JU16" s="1"/>
+      <c r="JV16" s="1"/>
+      <c r="JW16" s="1"/>
+      <c r="JX16" s="1"/>
+      <c r="JY16" s="1"/>
+      <c r="JZ16" s="1"/>
+      <c r="KA16" s="1"/>
+      <c r="KB16" s="1"/>
+      <c r="KC16" s="1"/>
+      <c r="KD16" s="1"/>
+      <c r="KE16" s="1"/>
+      <c r="KF16" s="1"/>
+      <c r="KG16" s="1"/>
+      <c r="KH16" s="1"/>
+      <c r="KI16" s="1"/>
+      <c r="KJ16" s="1"/>
+      <c r="KK16" s="1"/>
+      <c r="KL16" s="1"/>
+      <c r="KM16" s="1"/>
+      <c r="KN16" s="1"/>
+      <c r="KO16" s="1"/>
+      <c r="KP16" s="1"/>
+      <c r="KQ16" s="1"/>
+      <c r="KR16" s="1"/>
+      <c r="KS16" s="1"/>
+      <c r="KT16" s="1"/>
+      <c r="KU16" s="1"/>
+      <c r="KV16" s="1"/>
+      <c r="KW16" s="1"/>
+      <c r="KX16" s="1"/>
+      <c r="KY16" s="1"/>
+      <c r="KZ16" s="1"/>
+      <c r="LA16" s="1"/>
+      <c r="LB16" s="1"/>
+      <c r="LC16" s="1"/>
+      <c r="LD16" s="1"/>
+      <c r="LE16" s="1"/>
+      <c r="LF16" s="1"/>
+      <c r="LG16" s="1"/>
+      <c r="LH16" s="1"/>
+      <c r="LI16" s="1"/>
+      <c r="LJ16" s="1"/>
+      <c r="LK16" s="1"/>
+      <c r="LL16" s="1"/>
+      <c r="LM16" s="1"/>
+      <c r="LN16" s="1"/>
+      <c r="LO16" s="1"/>
+      <c r="LP16" s="1"/>
+      <c r="LQ16" s="1"/>
+      <c r="LR16" s="1"/>
+      <c r="LS16" s="1"/>
+      <c r="LT16" s="1"/>
+      <c r="LU16" s="1"/>
+      <c r="LV16" s="1"/>
+      <c r="LW16" s="1"/>
+      <c r="LX16" s="1"/>
+      <c r="LY16" s="1"/>
+      <c r="LZ16" s="1"/>
+      <c r="MA16" s="1"/>
+      <c r="MB16" s="1"/>
+      <c r="MC16" s="1"/>
+      <c r="MD16" s="1"/>
+      <c r="ME16" s="1"/>
+      <c r="MF16" s="1"/>
+      <c r="MG16" s="1"/>
+      <c r="MH16" s="1"/>
+      <c r="MI16" s="1"/>
+      <c r="MJ16" s="1"/>
+      <c r="MK16" s="1"/>
+      <c r="ML16" s="1"/>
+      <c r="MM16" s="1"/>
+      <c r="MN16" s="1"/>
+      <c r="MO16" s="1"/>
+      <c r="MP16" s="1"/>
+      <c r="MQ16" s="1"/>
+      <c r="MR16" s="1"/>
+      <c r="MS16" s="1"/>
+      <c r="MT16" s="1"/>
+      <c r="MU16" s="1"/>
+      <c r="MV16" s="1"/>
+      <c r="MW16" s="1"/>
+      <c r="MX16" s="1"/>
+      <c r="MY16" s="1"/>
+      <c r="MZ16" s="1"/>
+      <c r="NA16" s="1"/>
+      <c r="NB16" s="1"/>
+      <c r="NC16" s="1"/>
+      <c r="ND16" s="1"/>
+      <c r="NE16" s="1"/>
+      <c r="NF16" s="1"/>
+      <c r="NG16" s="1"/>
+      <c r="NH16" s="1"/>
+      <c r="NI16" s="1"/>
+      <c r="NJ16" s="1"/>
+      <c r="NK16" s="1"/>
+      <c r="NL16" s="1"/>
+      <c r="NM16" s="1"/>
+      <c r="NN16" s="1"/>
+      <c r="NO16" s="1"/>
+      <c r="NP16" s="1"/>
+      <c r="NQ16" s="1"/>
+      <c r="NR16" s="1"/>
+      <c r="NS16" s="1"/>
+      <c r="NT16" s="1"/>
+      <c r="NU16" s="1"/>
+      <c r="NV16" s="1"/>
+      <c r="NW16" s="1"/>
+      <c r="NX16" s="1"/>
+      <c r="NY16" s="1"/>
+      <c r="NZ16" s="1"/>
+      <c r="OA16" s="1"/>
+      <c r="OB16" s="1"/>
+      <c r="OC16" s="1"/>
+      <c r="OD16" s="1"/>
+      <c r="OE16" s="1"/>
+      <c r="OF16" s="1"/>
+      <c r="OG16" s="1"/>
+      <c r="OH16" s="1"/>
+      <c r="OI16" s="1"/>
+      <c r="OJ16" s="1"/>
+      <c r="OK16" s="1"/>
+      <c r="OL16" s="1"/>
+      <c r="OM16" s="1"/>
+      <c r="ON16" s="1"/>
+      <c r="OO16" s="1"/>
+      <c r="OP16" s="1"/>
+      <c r="OQ16" s="1"/>
+      <c r="OR16" s="1"/>
+      <c r="OS16" s="1"/>
+      <c r="OT16" s="1"/>
+      <c r="OU16" s="1"/>
+      <c r="OV16" s="1"/>
+      <c r="OW16" s="1"/>
+      <c r="OX16" s="1"/>
+      <c r="OY16" s="1"/>
+      <c r="OZ16" s="1"/>
+      <c r="PA16" s="1"/>
+      <c r="PB16" s="1"/>
+      <c r="PC16" s="1"/>
+      <c r="PD16" s="1"/>
+      <c r="PE16" s="1"/>
+      <c r="PF16" s="1"/>
+      <c r="PG16" s="1"/>
+      <c r="PH16" s="1"/>
+      <c r="PI16" s="1"/>
+      <c r="PJ16" s="1"/>
+      <c r="PK16" s="1"/>
+      <c r="PL16" s="1"/>
+      <c r="PM16" s="1"/>
+      <c r="PN16" s="1"/>
+      <c r="PO16" s="1"/>
+      <c r="PP16" s="1"/>
+      <c r="PQ16" s="1"/>
+      <c r="PR16" s="1"/>
+      <c r="PS16" s="1"/>
+      <c r="PT16" s="1"/>
+      <c r="PU16" s="1"/>
+      <c r="PV16" s="1"/>
+      <c r="PW16" s="1"/>
+      <c r="PX16" s="1"/>
+      <c r="PY16" s="1"/>
+      <c r="PZ16" s="1"/>
+      <c r="QA16" s="1"/>
+      <c r="QB16" s="1"/>
+      <c r="QC16" s="1"/>
+      <c r="QD16" s="1"/>
+      <c r="QE16" s="1"/>
+      <c r="QF16" s="1"/>
+      <c r="QG16" s="1"/>
+      <c r="QH16" s="1"/>
+      <c r="QI16" s="1"/>
+      <c r="QJ16" s="1"/>
+      <c r="QK16" s="1"/>
+      <c r="QL16" s="1"/>
+      <c r="QM16" s="1"/>
+      <c r="QN16" s="1"/>
+      <c r="QO16" s="1"/>
+      <c r="QP16" s="1"/>
+      <c r="QQ16" s="1"/>
+      <c r="QR16" s="1"/>
+      <c r="QS16" s="1"/>
+      <c r="QT16" s="1"/>
+      <c r="QU16" s="1"/>
+      <c r="QV16" s="1"/>
+      <c r="QW16" s="1"/>
+      <c r="QX16" s="1"/>
+      <c r="QY16" s="1"/>
+      <c r="QZ16" s="1"/>
+      <c r="RA16" s="1"/>
+      <c r="RB16" s="1"/>
+      <c r="RC16" s="1"/>
+      <c r="RD16" s="1"/>
+      <c r="RE16" s="1"/>
+      <c r="RF16" s="1"/>
+      <c r="RG16" s="1"/>
+      <c r="RH16" s="1"/>
+      <c r="RI16" s="1"/>
+      <c r="RJ16" s="1"/>
+      <c r="RK16" s="1"/>
+      <c r="RL16" s="1"/>
+      <c r="RM16" s="1"/>
+      <c r="RN16" s="1"/>
+      <c r="RO16" s="1"/>
+      <c r="RP16" s="1"/>
+      <c r="RQ16" s="1"/>
+      <c r="RR16" s="1"/>
+      <c r="RS16" s="1"/>
+      <c r="RT16" s="1"/>
+      <c r="RU16" s="1"/>
+      <c r="RV16" s="1"/>
+      <c r="RW16" s="1"/>
+      <c r="RX16" s="1"/>
+      <c r="RY16" s="1"/>
+      <c r="RZ16" s="1"/>
+      <c r="SA16" s="1"/>
+      <c r="SB16" s="1"/>
+      <c r="SC16" s="1"/>
+      <c r="SD16" s="1"/>
+      <c r="SE16" s="1"/>
+      <c r="SF16" s="1"/>
+      <c r="SG16" s="1"/>
+      <c r="SH16" s="1"/>
+      <c r="SI16" s="1"/>
+      <c r="SJ16" s="1"/>
+      <c r="SK16" s="1"/>
+      <c r="SL16" s="1"/>
+      <c r="SM16" s="1"/>
+      <c r="SN16" s="1"/>
+      <c r="SO16" s="1"/>
+      <c r="SP16" s="1"/>
+      <c r="SQ16" s="1"/>
+      <c r="SR16" s="1"/>
+      <c r="SS16" s="1"/>
+      <c r="ST16" s="1"/>
+      <c r="SU16" s="1"/>
+      <c r="SV16" s="1"/>
+      <c r="SW16" s="1"/>
+      <c r="SX16" s="1"/>
+      <c r="SY16" s="1"/>
+      <c r="SZ16" s="1"/>
+      <c r="TA16" s="1"/>
+      <c r="TB16" s="1"/>
+      <c r="TC16" s="1"/>
+      <c r="TD16" s="1"/>
+      <c r="TE16" s="1"/>
+      <c r="TF16" s="1"/>
+      <c r="TG16" s="1"/>
+      <c r="TH16" s="1"/>
+      <c r="TI16" s="1"/>
+      <c r="TJ16" s="1"/>
+      <c r="TK16" s="1"/>
+      <c r="TL16" s="1"/>
+      <c r="TM16" s="1"/>
+      <c r="TN16" s="1"/>
+      <c r="TO16" s="1"/>
+      <c r="TP16" s="1"/>
+      <c r="TQ16" s="1"/>
+      <c r="TR16" s="1"/>
+      <c r="TS16" s="1"/>
+      <c r="TT16" s="1"/>
+      <c r="TU16" s="1"/>
+      <c r="TV16" s="1"/>
+      <c r="TW16" s="1"/>
+      <c r="TX16" s="1"/>
+      <c r="TY16" s="1"/>
+      <c r="TZ16" s="1"/>
+    </row>
+    <row r="17" spans="1:546" s="47" customFormat="1" ht="92.25" customHeight="1" thickBot="1">
+      <c r="A17" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" s="55">
+        <v>2026</v>
+      </c>
+      <c r="E17" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="G17" s="56">
+        <v>46084</v>
+      </c>
+      <c r="H17" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" s="55" t="s">
+        <v>185</v>
+      </c>
+      <c r="J17" s="55" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="M17" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="N17" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="O17" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="P17" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q17" s="79" t="s">
+        <v>274</v>
+      </c>
+      <c r="R17" s="68" t="s">
+        <v>320</v>
+      </c>
+      <c r="S17" s="68" t="s">
+        <v>321</v>
+      </c>
+      <c r="T17" s="68" t="s">
+        <v>322</v>
+      </c>
+      <c r="U17" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="V17" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W17" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="X17" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+      <c r="AI17" s="1"/>
+      <c r="AJ17" s="1"/>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="1"/>
+      <c r="AO17" s="1"/>
+      <c r="AP17" s="1"/>
+      <c r="AQ17" s="1"/>
+      <c r="AR17" s="1"/>
+      <c r="AS17" s="1"/>
+      <c r="AT17" s="1"/>
+      <c r="AU17" s="1"/>
+      <c r="AV17" s="1"/>
+      <c r="AW17" s="1"/>
+      <c r="AX17" s="1"/>
+      <c r="AY17" s="1"/>
+      <c r="AZ17" s="1"/>
+      <c r="BA17" s="1"/>
+      <c r="BB17" s="1"/>
+      <c r="BC17" s="1"/>
+      <c r="BD17" s="1"/>
+      <c r="BE17" s="1"/>
+      <c r="BF17" s="1"/>
+      <c r="BG17" s="1"/>
+      <c r="BH17" s="1"/>
+      <c r="BI17" s="1"/>
+      <c r="BJ17" s="1"/>
+      <c r="BK17" s="1"/>
+      <c r="BL17" s="1"/>
+      <c r="BM17" s="1"/>
+      <c r="BN17" s="1"/>
+      <c r="BO17" s="1"/>
+      <c r="BP17" s="1"/>
+      <c r="BQ17" s="1"/>
+      <c r="BR17" s="1"/>
+      <c r="BS17" s="1"/>
+      <c r="BT17" s="1"/>
+      <c r="BU17" s="1"/>
+      <c r="BV17" s="1"/>
+      <c r="BW17" s="1"/>
+      <c r="BX17" s="1"/>
+      <c r="BY17" s="1"/>
+      <c r="BZ17" s="1"/>
+      <c r="CA17" s="1"/>
+      <c r="CB17" s="1"/>
+      <c r="CC17" s="1"/>
+      <c r="CD17" s="1"/>
+      <c r="CE17" s="1"/>
+      <c r="CF17" s="1"/>
+      <c r="CG17" s="1"/>
+      <c r="CH17" s="1"/>
+      <c r="CI17" s="1"/>
+      <c r="CJ17" s="1"/>
+      <c r="CK17" s="1"/>
+      <c r="CL17" s="1"/>
+      <c r="CM17" s="1"/>
+      <c r="CN17" s="1"/>
+      <c r="CO17" s="1"/>
+      <c r="CP17" s="1"/>
+      <c r="CQ17" s="1"/>
+      <c r="CR17" s="1"/>
+      <c r="CS17" s="1"/>
+      <c r="CT17" s="1"/>
+      <c r="CU17" s="1"/>
+      <c r="CV17" s="1"/>
+      <c r="CW17" s="1"/>
+      <c r="CX17" s="1"/>
+      <c r="CY17" s="1"/>
+      <c r="CZ17" s="1"/>
+      <c r="DA17" s="1"/>
+      <c r="DB17" s="1"/>
+      <c r="DC17" s="1"/>
+      <c r="DD17" s="1"/>
+      <c r="DE17" s="1"/>
+      <c r="DF17" s="1"/>
+      <c r="DG17" s="1"/>
+      <c r="DH17" s="1"/>
+      <c r="DI17" s="1"/>
+      <c r="DJ17" s="1"/>
+      <c r="DK17" s="1"/>
+      <c r="DL17" s="1"/>
+      <c r="DM17" s="1"/>
+      <c r="DN17" s="1"/>
+      <c r="DO17" s="1"/>
+      <c r="DP17" s="1"/>
+      <c r="DQ17" s="1"/>
+      <c r="DR17" s="1"/>
+      <c r="DS17" s="1"/>
+      <c r="DT17" s="1"/>
+      <c r="DU17" s="1"/>
+      <c r="DV17" s="1"/>
+      <c r="DW17" s="1"/>
+      <c r="DX17" s="1"/>
+      <c r="DY17" s="1"/>
+      <c r="DZ17" s="1"/>
+      <c r="EA17" s="1"/>
+      <c r="EB17" s="1"/>
+      <c r="EC17" s="1"/>
+      <c r="ED17" s="1"/>
+      <c r="EE17" s="1"/>
+      <c r="EF17" s="1"/>
+      <c r="EG17" s="1"/>
+      <c r="EH17" s="1"/>
+      <c r="EI17" s="1"/>
+      <c r="EJ17" s="1"/>
+      <c r="EK17" s="1"/>
+      <c r="EL17" s="1"/>
+      <c r="EM17" s="1"/>
+      <c r="EN17" s="1"/>
+      <c r="EO17" s="1"/>
+      <c r="EP17" s="1"/>
+      <c r="EQ17" s="1"/>
+      <c r="ER17" s="1"/>
+      <c r="ES17" s="1"/>
+      <c r="ET17" s="1"/>
+      <c r="EU17" s="1"/>
+      <c r="EV17" s="1"/>
+      <c r="EW17" s="1"/>
+      <c r="EX17" s="1"/>
+      <c r="EY17" s="1"/>
+      <c r="EZ17" s="1"/>
+      <c r="FA17" s="1"/>
+      <c r="FB17" s="1"/>
+      <c r="FC17" s="1"/>
+      <c r="FD17" s="1"/>
+      <c r="FE17" s="1"/>
+      <c r="FF17" s="1"/>
+      <c r="FG17" s="1"/>
+      <c r="FH17" s="1"/>
+      <c r="FI17" s="1"/>
+      <c r="FJ17" s="1"/>
+      <c r="FK17" s="1"/>
+      <c r="FL17" s="1"/>
+      <c r="FM17" s="1"/>
+      <c r="FN17" s="1"/>
+      <c r="FO17" s="1"/>
+      <c r="FP17" s="1"/>
+      <c r="FQ17" s="1"/>
+      <c r="FR17" s="1"/>
+      <c r="FS17" s="1"/>
+      <c r="FT17" s="1"/>
+      <c r="FU17" s="1"/>
+      <c r="FV17" s="1"/>
+      <c r="FW17" s="1"/>
+      <c r="FX17" s="1"/>
+      <c r="FY17" s="1"/>
+      <c r="FZ17" s="1"/>
+      <c r="GA17" s="1"/>
+      <c r="GB17" s="1"/>
+      <c r="GC17" s="1"/>
+      <c r="GD17" s="1"/>
+      <c r="GE17" s="1"/>
+      <c r="GF17" s="1"/>
+      <c r="GG17" s="1"/>
+      <c r="GH17" s="1"/>
+      <c r="GI17" s="1"/>
+      <c r="GJ17" s="1"/>
+      <c r="GK17" s="1"/>
+      <c r="GL17" s="1"/>
+      <c r="GM17" s="1"/>
+      <c r="GN17" s="1"/>
+      <c r="GO17" s="1"/>
+      <c r="GP17" s="1"/>
+      <c r="GQ17" s="1"/>
+      <c r="GR17" s="1"/>
+      <c r="GS17" s="1"/>
+      <c r="GT17" s="1"/>
+      <c r="GU17" s="1"/>
+      <c r="GV17" s="1"/>
+      <c r="GW17" s="1"/>
+      <c r="GX17" s="1"/>
+      <c r="GY17" s="1"/>
+      <c r="GZ17" s="1"/>
+      <c r="HA17" s="1"/>
+      <c r="HB17" s="1"/>
+      <c r="HC17" s="1"/>
+      <c r="HD17" s="1"/>
+      <c r="HE17" s="1"/>
+      <c r="HF17" s="1"/>
+      <c r="HG17" s="1"/>
+      <c r="HH17" s="1"/>
+      <c r="HI17" s="1"/>
+      <c r="HJ17" s="1"/>
+      <c r="HK17" s="1"/>
+      <c r="HL17" s="1"/>
+      <c r="HM17" s="1"/>
+      <c r="HN17" s="1"/>
+      <c r="HO17" s="1"/>
+      <c r="HP17" s="1"/>
+      <c r="HQ17" s="1"/>
+      <c r="HR17" s="1"/>
+      <c r="HS17" s="1"/>
+      <c r="HT17" s="1"/>
+      <c r="HU17" s="1"/>
+      <c r="HV17" s="1"/>
+      <c r="HW17" s="1"/>
+      <c r="HX17" s="1"/>
+      <c r="HY17" s="1"/>
+      <c r="HZ17" s="1"/>
+      <c r="IA17" s="1"/>
+      <c r="IB17" s="1"/>
+      <c r="IC17" s="1"/>
+      <c r="ID17" s="1"/>
+      <c r="IE17" s="1"/>
+      <c r="IF17" s="1"/>
+      <c r="IG17" s="1"/>
+      <c r="IH17" s="1"/>
+      <c r="II17" s="1"/>
+      <c r="IJ17" s="1"/>
+      <c r="IK17" s="1"/>
+      <c r="IL17" s="1"/>
+      <c r="IM17" s="1"/>
+      <c r="IN17" s="1"/>
+      <c r="IO17" s="1"/>
+      <c r="IP17" s="1"/>
+      <c r="IQ17" s="1"/>
+      <c r="IR17" s="1"/>
+      <c r="IS17" s="1"/>
+      <c r="IT17" s="1"/>
+      <c r="IU17" s="1"/>
+      <c r="IV17" s="1"/>
+      <c r="IW17" s="1"/>
+      <c r="IX17" s="1"/>
+      <c r="IY17" s="1"/>
+      <c r="IZ17" s="1"/>
+      <c r="JA17" s="1"/>
+      <c r="JB17" s="1"/>
+      <c r="JC17" s="1"/>
+      <c r="JD17" s="1"/>
+      <c r="JE17" s="1"/>
+      <c r="JF17" s="1"/>
+      <c r="JG17" s="1"/>
+      <c r="JH17" s="1"/>
+      <c r="JI17" s="1"/>
+      <c r="JJ17" s="1"/>
+      <c r="JK17" s="1"/>
+      <c r="JL17" s="1"/>
+      <c r="JM17" s="1"/>
+      <c r="JN17" s="1"/>
+      <c r="JO17" s="1"/>
+      <c r="JP17" s="1"/>
+      <c r="JQ17" s="1"/>
+      <c r="JR17" s="1"/>
+      <c r="JS17" s="1"/>
+      <c r="JT17" s="1"/>
+      <c r="JU17" s="1"/>
+      <c r="JV17" s="1"/>
+      <c r="JW17" s="1"/>
+      <c r="JX17" s="1"/>
+      <c r="JY17" s="1"/>
+      <c r="JZ17" s="1"/>
+      <c r="KA17" s="1"/>
+      <c r="KB17" s="1"/>
+      <c r="KC17" s="1"/>
+      <c r="KD17" s="1"/>
+      <c r="KE17" s="1"/>
+      <c r="KF17" s="1"/>
+      <c r="KG17" s="1"/>
+      <c r="KH17" s="1"/>
+      <c r="KI17" s="1"/>
+      <c r="KJ17" s="1"/>
+      <c r="KK17" s="1"/>
+      <c r="KL17" s="1"/>
+      <c r="KM17" s="1"/>
+      <c r="KN17" s="1"/>
+      <c r="KO17" s="1"/>
+      <c r="KP17" s="1"/>
+      <c r="KQ17" s="1"/>
+      <c r="KR17" s="1"/>
+      <c r="KS17" s="1"/>
+      <c r="KT17" s="1"/>
+      <c r="KU17" s="1"/>
+      <c r="KV17" s="1"/>
+      <c r="KW17" s="1"/>
+      <c r="KX17" s="1"/>
+      <c r="KY17" s="1"/>
+      <c r="KZ17" s="1"/>
+      <c r="LA17" s="1"/>
+      <c r="LB17" s="1"/>
+      <c r="LC17" s="1"/>
+      <c r="LD17" s="1"/>
+      <c r="LE17" s="1"/>
+      <c r="LF17" s="1"/>
+      <c r="LG17" s="1"/>
+      <c r="LH17" s="1"/>
+      <c r="LI17" s="1"/>
+      <c r="LJ17" s="1"/>
+      <c r="LK17" s="1"/>
+      <c r="LL17" s="1"/>
+      <c r="LM17" s="1"/>
+      <c r="LN17" s="1"/>
+      <c r="LO17" s="1"/>
+      <c r="LP17" s="1"/>
+      <c r="LQ17" s="1"/>
+      <c r="LR17" s="1"/>
+      <c r="LS17" s="1"/>
+      <c r="LT17" s="1"/>
+      <c r="LU17" s="1"/>
+      <c r="LV17" s="1"/>
+      <c r="LW17" s="1"/>
+      <c r="LX17" s="1"/>
+      <c r="LY17" s="1"/>
+      <c r="LZ17" s="1"/>
+      <c r="MA17" s="1"/>
+      <c r="MB17" s="1"/>
+      <c r="MC17" s="1"/>
+      <c r="MD17" s="1"/>
+      <c r="ME17" s="1"/>
+      <c r="MF17" s="1"/>
+      <c r="MG17" s="1"/>
+      <c r="MH17" s="1"/>
+      <c r="MI17" s="1"/>
+      <c r="MJ17" s="1"/>
+      <c r="MK17" s="1"/>
+      <c r="ML17" s="1"/>
+      <c r="MM17" s="1"/>
+      <c r="MN17" s="1"/>
+      <c r="MO17" s="1"/>
+      <c r="MP17" s="1"/>
+      <c r="MQ17" s="1"/>
+      <c r="MR17" s="1"/>
+      <c r="MS17" s="1"/>
+      <c r="MT17" s="1"/>
+      <c r="MU17" s="1"/>
+      <c r="MV17" s="1"/>
+      <c r="MW17" s="1"/>
+      <c r="MX17" s="1"/>
+      <c r="MY17" s="1"/>
+      <c r="MZ17" s="1"/>
+      <c r="NA17" s="1"/>
+      <c r="NB17" s="1"/>
+      <c r="NC17" s="1"/>
+      <c r="ND17" s="1"/>
+      <c r="NE17" s="1"/>
+      <c r="NF17" s="1"/>
+      <c r="NG17" s="1"/>
+      <c r="NH17" s="1"/>
+      <c r="NI17" s="1"/>
+      <c r="NJ17" s="1"/>
+      <c r="NK17" s="1"/>
+      <c r="NL17" s="1"/>
+      <c r="NM17" s="1"/>
+      <c r="NN17" s="1"/>
+      <c r="NO17" s="1"/>
+      <c r="NP17" s="1"/>
+      <c r="NQ17" s="1"/>
+      <c r="NR17" s="1"/>
+      <c r="NS17" s="1"/>
+      <c r="NT17" s="1"/>
+      <c r="NU17" s="1"/>
+      <c r="NV17" s="1"/>
+      <c r="NW17" s="1"/>
+      <c r="NX17" s="1"/>
+      <c r="NY17" s="1"/>
+      <c r="NZ17" s="1"/>
+      <c r="OA17" s="1"/>
+      <c r="OB17" s="1"/>
+      <c r="OC17" s="1"/>
+      <c r="OD17" s="1"/>
+      <c r="OE17" s="1"/>
+      <c r="OF17" s="1"/>
+      <c r="OG17" s="1"/>
+      <c r="OH17" s="1"/>
+      <c r="OI17" s="1"/>
+      <c r="OJ17" s="1"/>
+      <c r="OK17" s="1"/>
+      <c r="OL17" s="1"/>
+      <c r="OM17" s="1"/>
+      <c r="ON17" s="1"/>
+      <c r="OO17" s="1"/>
+      <c r="OP17" s="1"/>
+      <c r="OQ17" s="1"/>
+      <c r="OR17" s="1"/>
+      <c r="OS17" s="1"/>
+      <c r="OT17" s="1"/>
+      <c r="OU17" s="1"/>
+      <c r="OV17" s="1"/>
+      <c r="OW17" s="1"/>
+      <c r="OX17" s="1"/>
+      <c r="OY17" s="1"/>
+      <c r="OZ17" s="1"/>
+      <c r="PA17" s="1"/>
+      <c r="PB17" s="1"/>
+      <c r="PC17" s="1"/>
+      <c r="PD17" s="1"/>
+      <c r="PE17" s="1"/>
+      <c r="PF17" s="1"/>
+      <c r="PG17" s="1"/>
+      <c r="PH17" s="1"/>
+      <c r="PI17" s="1"/>
+      <c r="PJ17" s="1"/>
+      <c r="PK17" s="1"/>
+      <c r="PL17" s="1"/>
+      <c r="PM17" s="1"/>
+      <c r="PN17" s="1"/>
+      <c r="PO17" s="1"/>
+      <c r="PP17" s="1"/>
+      <c r="PQ17" s="1"/>
+      <c r="PR17" s="1"/>
+      <c r="PS17" s="1"/>
+      <c r="PT17" s="1"/>
+      <c r="PU17" s="1"/>
+      <c r="PV17" s="1"/>
+      <c r="PW17" s="1"/>
+      <c r="PX17" s="1"/>
+      <c r="PY17" s="1"/>
+      <c r="PZ17" s="1"/>
+      <c r="QA17" s="1"/>
+      <c r="QB17" s="1"/>
+      <c r="QC17" s="1"/>
+      <c r="QD17" s="1"/>
+      <c r="QE17" s="1"/>
+      <c r="QF17" s="1"/>
+      <c r="QG17" s="1"/>
+      <c r="QH17" s="1"/>
+      <c r="QI17" s="1"/>
+      <c r="QJ17" s="1"/>
+      <c r="QK17" s="1"/>
+      <c r="QL17" s="1"/>
+      <c r="QM17" s="1"/>
+      <c r="QN17" s="1"/>
+      <c r="QO17" s="1"/>
+      <c r="QP17" s="1"/>
+      <c r="QQ17" s="1"/>
+      <c r="QR17" s="1"/>
+      <c r="QS17" s="1"/>
+      <c r="QT17" s="1"/>
+      <c r="QU17" s="1"/>
+      <c r="QV17" s="1"/>
+      <c r="QW17" s="1"/>
+      <c r="QX17" s="1"/>
+      <c r="QY17" s="1"/>
+      <c r="QZ17" s="1"/>
+      <c r="RA17" s="1"/>
+      <c r="RB17" s="1"/>
+      <c r="RC17" s="1"/>
+      <c r="RD17" s="1"/>
+      <c r="RE17" s="1"/>
+      <c r="RF17" s="1"/>
+      <c r="RG17" s="1"/>
+      <c r="RH17" s="1"/>
+      <c r="RI17" s="1"/>
+      <c r="RJ17" s="1"/>
+      <c r="RK17" s="1"/>
+      <c r="RL17" s="1"/>
+      <c r="RM17" s="1"/>
+      <c r="RN17" s="1"/>
+      <c r="RO17" s="1"/>
+      <c r="RP17" s="1"/>
+      <c r="RQ17" s="1"/>
+      <c r="RR17" s="1"/>
+      <c r="RS17" s="1"/>
+      <c r="RT17" s="1"/>
+      <c r="RU17" s="1"/>
+      <c r="RV17" s="1"/>
+      <c r="RW17" s="1"/>
+      <c r="RX17" s="1"/>
+      <c r="RY17" s="1"/>
+      <c r="RZ17" s="1"/>
+      <c r="SA17" s="1"/>
+      <c r="SB17" s="1"/>
+      <c r="SC17" s="1"/>
+      <c r="SD17" s="1"/>
+      <c r="SE17" s="1"/>
+      <c r="SF17" s="1"/>
+      <c r="SG17" s="1"/>
+      <c r="SH17" s="1"/>
+      <c r="SI17" s="1"/>
+      <c r="SJ17" s="1"/>
+      <c r="SK17" s="1"/>
+      <c r="SL17" s="1"/>
+      <c r="SM17" s="1"/>
+      <c r="SN17" s="1"/>
+      <c r="SO17" s="1"/>
+      <c r="SP17" s="1"/>
+      <c r="SQ17" s="1"/>
+      <c r="SR17" s="1"/>
+      <c r="SS17" s="1"/>
+      <c r="ST17" s="1"/>
+      <c r="SU17" s="1"/>
+      <c r="SV17" s="1"/>
+      <c r="SW17" s="1"/>
+      <c r="SX17" s="1"/>
+      <c r="SY17" s="1"/>
+      <c r="SZ17" s="1"/>
+      <c r="TA17" s="1"/>
+      <c r="TB17" s="1"/>
+      <c r="TC17" s="1"/>
+      <c r="TD17" s="1"/>
+      <c r="TE17" s="1"/>
+      <c r="TF17" s="1"/>
+      <c r="TG17" s="1"/>
+      <c r="TH17" s="1"/>
+      <c r="TI17" s="1"/>
+      <c r="TJ17" s="1"/>
+      <c r="TK17" s="1"/>
+      <c r="TL17" s="1"/>
+      <c r="TM17" s="1"/>
+      <c r="TN17" s="1"/>
+      <c r="TO17" s="1"/>
+      <c r="TP17" s="1"/>
+      <c r="TQ17" s="1"/>
+      <c r="TR17" s="1"/>
+      <c r="TS17" s="1"/>
+      <c r="TT17" s="1"/>
+      <c r="TU17" s="1"/>
+      <c r="TV17" s="1"/>
+      <c r="TW17" s="1"/>
+      <c r="TX17" s="1"/>
+      <c r="TY17" s="1"/>
+      <c r="TZ17" s="1"/>
+    </row>
+    <row r="18" spans="1:546" s="47" customFormat="1" ht="90" customHeight="1" thickBot="1">
+      <c r="A18" s="60" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E18" s="62">
+        <v>46212</v>
+      </c>
+      <c r="F18" s="62">
+        <v>46333</v>
+      </c>
+      <c r="G18" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="M18" s="64" t="s">
+        <v>205</v>
+      </c>
+      <c r="N18" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="O18" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="P18" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q18" s="79" t="s">
+        <v>324</v>
+      </c>
+      <c r="R18" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="S18" s="68" t="s">
+        <v>326</v>
+      </c>
+      <c r="T18" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="U18" s="68" t="s">
+        <v>327</v>
+      </c>
+      <c r="V18" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W18" s="67" t="s">
+        <v>328</v>
+      </c>
+      <c r="X18" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1"/>
+      <c r="AJ18" s="1"/>
+      <c r="AK18" s="1"/>
+      <c r="AL18" s="1"/>
+      <c r="AM18" s="1"/>
+      <c r="AN18" s="1"/>
+      <c r="AO18" s="1"/>
+      <c r="AP18" s="1"/>
+      <c r="AQ18" s="1"/>
+      <c r="AR18" s="1"/>
+      <c r="AS18" s="1"/>
+      <c r="AT18" s="1"/>
+      <c r="AU18" s="1"/>
+      <c r="AV18" s="1"/>
+      <c r="AW18" s="1"/>
+      <c r="AX18" s="1"/>
+      <c r="AY18" s="1"/>
+      <c r="AZ18" s="1"/>
+      <c r="BA18" s="1"/>
+      <c r="BB18" s="1"/>
+      <c r="BC18" s="1"/>
+      <c r="BD18" s="1"/>
+      <c r="BE18" s="1"/>
+      <c r="BF18" s="1"/>
+      <c r="BG18" s="1"/>
+      <c r="BH18" s="1"/>
+      <c r="BI18" s="1"/>
+      <c r="BJ18" s="1"/>
+      <c r="BK18" s="1"/>
+      <c r="BL18" s="1"/>
+      <c r="BM18" s="1"/>
+      <c r="BN18" s="1"/>
+      <c r="BO18" s="1"/>
+      <c r="BP18" s="1"/>
+      <c r="BQ18" s="1"/>
+      <c r="BR18" s="1"/>
+      <c r="BS18" s="1"/>
+      <c r="BT18" s="1"/>
+      <c r="BU18" s="1"/>
+      <c r="BV18" s="1"/>
+      <c r="BW18" s="1"/>
+      <c r="BX18" s="1"/>
+      <c r="BY18" s="1"/>
+      <c r="BZ18" s="1"/>
+      <c r="CA18" s="1"/>
+      <c r="CB18" s="1"/>
+      <c r="CC18" s="1"/>
+      <c r="CD18" s="1"/>
+      <c r="CE18" s="1"/>
+      <c r="CF18" s="1"/>
+      <c r="CG18" s="1"/>
+      <c r="CH18" s="1"/>
+      <c r="CI18" s="1"/>
+      <c r="CJ18" s="1"/>
+      <c r="CK18" s="1"/>
+      <c r="CL18" s="1"/>
+      <c r="CM18" s="1"/>
+      <c r="CN18" s="1"/>
+      <c r="CO18" s="1"/>
+      <c r="CP18" s="1"/>
+      <c r="CQ18" s="1"/>
+      <c r="CR18" s="1"/>
+      <c r="CS18" s="1"/>
+      <c r="CT18" s="1"/>
+      <c r="CU18" s="1"/>
+      <c r="CV18" s="1"/>
+      <c r="CW18" s="1"/>
+      <c r="CX18" s="1"/>
+      <c r="CY18" s="1"/>
+      <c r="CZ18" s="1"/>
+      <c r="DA18" s="1"/>
+      <c r="DB18" s="1"/>
+      <c r="DC18" s="1"/>
+      <c r="DD18" s="1"/>
+      <c r="DE18" s="1"/>
+      <c r="DF18" s="1"/>
+      <c r="DG18" s="1"/>
+      <c r="DH18" s="1"/>
+      <c r="DI18" s="1"/>
+      <c r="DJ18" s="1"/>
+      <c r="DK18" s="1"/>
+      <c r="DL18" s="1"/>
+      <c r="DM18" s="1"/>
+      <c r="DN18" s="1"/>
+      <c r="DO18" s="1"/>
+      <c r="DP18" s="1"/>
+      <c r="DQ18" s="1"/>
+      <c r="DR18" s="1"/>
+      <c r="DS18" s="1"/>
+      <c r="DT18" s="1"/>
+      <c r="DU18" s="1"/>
+      <c r="DV18" s="1"/>
+      <c r="DW18" s="1"/>
+      <c r="DX18" s="1"/>
+      <c r="DY18" s="1"/>
+      <c r="DZ18" s="1"/>
+      <c r="EA18" s="1"/>
+      <c r="EB18" s="1"/>
+      <c r="EC18" s="1"/>
+      <c r="ED18" s="1"/>
+      <c r="EE18" s="1"/>
+      <c r="EF18" s="1"/>
+      <c r="EG18" s="1"/>
+      <c r="EH18" s="1"/>
+      <c r="EI18" s="1"/>
+      <c r="EJ18" s="1"/>
+      <c r="EK18" s="1"/>
+      <c r="EL18" s="1"/>
+      <c r="EM18" s="1"/>
+      <c r="EN18" s="1"/>
+      <c r="EO18" s="1"/>
+      <c r="EP18" s="1"/>
+      <c r="EQ18" s="1"/>
+      <c r="ER18" s="1"/>
+      <c r="ES18" s="1"/>
+      <c r="ET18" s="1"/>
+      <c r="EU18" s="1"/>
+      <c r="EV18" s="1"/>
+      <c r="EW18" s="1"/>
+      <c r="EX18" s="1"/>
+      <c r="EY18" s="1"/>
+      <c r="EZ18" s="1"/>
+      <c r="FA18" s="1"/>
+      <c r="FB18" s="1"/>
+      <c r="FC18" s="1"/>
+      <c r="FD18" s="1"/>
+      <c r="FE18" s="1"/>
+      <c r="FF18" s="1"/>
+      <c r="FG18" s="1"/>
+      <c r="FH18" s="1"/>
+      <c r="FI18" s="1"/>
+      <c r="FJ18" s="1"/>
+      <c r="FK18" s="1"/>
+      <c r="FL18" s="1"/>
+      <c r="FM18" s="1"/>
+      <c r="FN18" s="1"/>
+      <c r="FO18" s="1"/>
+      <c r="FP18" s="1"/>
+      <c r="FQ18" s="1"/>
+      <c r="FR18" s="1"/>
+      <c r="FS18" s="1"/>
+      <c r="FT18" s="1"/>
+      <c r="FU18" s="1"/>
+      <c r="FV18" s="1"/>
+      <c r="FW18" s="1"/>
+      <c r="FX18" s="1"/>
+      <c r="FY18" s="1"/>
+      <c r="FZ18" s="1"/>
+      <c r="GA18" s="1"/>
+      <c r="GB18" s="1"/>
+      <c r="GC18" s="1"/>
+      <c r="GD18" s="1"/>
+      <c r="GE18" s="1"/>
+      <c r="GF18" s="1"/>
+      <c r="GG18" s="1"/>
+      <c r="GH18" s="1"/>
+      <c r="GI18" s="1"/>
+      <c r="GJ18" s="1"/>
+      <c r="GK18" s="1"/>
+      <c r="GL18" s="1"/>
+      <c r="GM18" s="1"/>
+      <c r="GN18" s="1"/>
+      <c r="GO18" s="1"/>
+      <c r="GP18" s="1"/>
+      <c r="GQ18" s="1"/>
+      <c r="GR18" s="1"/>
+      <c r="GS18" s="1"/>
+      <c r="GT18" s="1"/>
+      <c r="GU18" s="1"/>
+      <c r="GV18" s="1"/>
+      <c r="GW18" s="1"/>
+      <c r="GX18" s="1"/>
+      <c r="GY18" s="1"/>
+      <c r="GZ18" s="1"/>
+      <c r="HA18" s="1"/>
+      <c r="HB18" s="1"/>
+      <c r="HC18" s="1"/>
+      <c r="HD18" s="1"/>
+      <c r="HE18" s="1"/>
+      <c r="HF18" s="1"/>
+      <c r="HG18" s="1"/>
+      <c r="HH18" s="1"/>
+      <c r="HI18" s="1"/>
+      <c r="HJ18" s="1"/>
+      <c r="HK18" s="1"/>
+      <c r="HL18" s="1"/>
+      <c r="HM18" s="1"/>
+      <c r="HN18" s="1"/>
+      <c r="HO18" s="1"/>
+      <c r="HP18" s="1"/>
+      <c r="HQ18" s="1"/>
+      <c r="HR18" s="1"/>
+      <c r="HS18" s="1"/>
+      <c r="HT18" s="1"/>
+      <c r="HU18" s="1"/>
+      <c r="HV18" s="1"/>
+      <c r="HW18" s="1"/>
+      <c r="HX18" s="1"/>
+      <c r="HY18" s="1"/>
+      <c r="HZ18" s="1"/>
+      <c r="IA18" s="1"/>
+      <c r="IB18" s="1"/>
+      <c r="IC18" s="1"/>
+      <c r="ID18" s="1"/>
+      <c r="IE18" s="1"/>
+      <c r="IF18" s="1"/>
+      <c r="IG18" s="1"/>
+      <c r="IH18" s="1"/>
+      <c r="II18" s="1"/>
+      <c r="IJ18" s="1"/>
+      <c r="IK18" s="1"/>
+      <c r="IL18" s="1"/>
+      <c r="IM18" s="1"/>
+      <c r="IN18" s="1"/>
+      <c r="IO18" s="1"/>
+      <c r="IP18" s="1"/>
+      <c r="IQ18" s="1"/>
+      <c r="IR18" s="1"/>
+      <c r="IS18" s="1"/>
+      <c r="IT18" s="1"/>
+      <c r="IU18" s="1"/>
+      <c r="IV18" s="1"/>
+      <c r="IW18" s="1"/>
+      <c r="IX18" s="1"/>
+      <c r="IY18" s="1"/>
+      <c r="IZ18" s="1"/>
+      <c r="JA18" s="1"/>
+      <c r="JB18" s="1"/>
+      <c r="JC18" s="1"/>
+      <c r="JD18" s="1"/>
+      <c r="JE18" s="1"/>
+      <c r="JF18" s="1"/>
+      <c r="JG18" s="1"/>
+      <c r="JH18" s="1"/>
+      <c r="JI18" s="1"/>
+      <c r="JJ18" s="1"/>
+      <c r="JK18" s="1"/>
+      <c r="JL18" s="1"/>
+      <c r="JM18" s="1"/>
+      <c r="JN18" s="1"/>
+      <c r="JO18" s="1"/>
+      <c r="JP18" s="1"/>
+      <c r="JQ18" s="1"/>
+      <c r="JR18" s="1"/>
+      <c r="JS18" s="1"/>
+      <c r="JT18" s="1"/>
+      <c r="JU18" s="1"/>
+      <c r="JV18" s="1"/>
+      <c r="JW18" s="1"/>
+      <c r="JX18" s="1"/>
+      <c r="JY18" s="1"/>
+      <c r="JZ18" s="1"/>
+      <c r="KA18" s="1"/>
+      <c r="KB18" s="1"/>
+      <c r="KC18" s="1"/>
+      <c r="KD18" s="1"/>
+      <c r="KE18" s="1"/>
+      <c r="KF18" s="1"/>
+      <c r="KG18" s="1"/>
+      <c r="KH18" s="1"/>
+      <c r="KI18" s="1"/>
+      <c r="KJ18" s="1"/>
+      <c r="KK18" s="1"/>
+      <c r="KL18" s="1"/>
+      <c r="KM18" s="1"/>
+      <c r="KN18" s="1"/>
+      <c r="KO18" s="1"/>
+      <c r="KP18" s="1"/>
+      <c r="KQ18" s="1"/>
+      <c r="KR18" s="1"/>
+      <c r="KS18" s="1"/>
+      <c r="KT18" s="1"/>
+      <c r="KU18" s="1"/>
+      <c r="KV18" s="1"/>
+      <c r="KW18" s="1"/>
+      <c r="KX18" s="1"/>
+      <c r="KY18" s="1"/>
+      <c r="KZ18" s="1"/>
+      <c r="LA18" s="1"/>
+      <c r="LB18" s="1"/>
+      <c r="LC18" s="1"/>
+      <c r="LD18" s="1"/>
+      <c r="LE18" s="1"/>
+      <c r="LF18" s="1"/>
+      <c r="LG18" s="1"/>
+      <c r="LH18" s="1"/>
+      <c r="LI18" s="1"/>
+      <c r="LJ18" s="1"/>
+      <c r="LK18" s="1"/>
+      <c r="LL18" s="1"/>
+      <c r="LM18" s="1"/>
+      <c r="LN18" s="1"/>
+      <c r="LO18" s="1"/>
+      <c r="LP18" s="1"/>
+      <c r="LQ18" s="1"/>
+      <c r="LR18" s="1"/>
+      <c r="LS18" s="1"/>
+      <c r="LT18" s="1"/>
+      <c r="LU18" s="1"/>
+      <c r="LV18" s="1"/>
+      <c r="LW18" s="1"/>
+      <c r="LX18" s="1"/>
+      <c r="LY18" s="1"/>
+      <c r="LZ18" s="1"/>
+      <c r="MA18" s="1"/>
+      <c r="MB18" s="1"/>
+      <c r="MC18" s="1"/>
+      <c r="MD18" s="1"/>
+      <c r="ME18" s="1"/>
+      <c r="MF18" s="1"/>
+      <c r="MG18" s="1"/>
+      <c r="MH18" s="1"/>
+      <c r="MI18" s="1"/>
+      <c r="MJ18" s="1"/>
+      <c r="MK18" s="1"/>
+      <c r="ML18" s="1"/>
+      <c r="MM18" s="1"/>
+      <c r="MN18" s="1"/>
+      <c r="MO18" s="1"/>
+      <c r="MP18" s="1"/>
+      <c r="MQ18" s="1"/>
+      <c r="MR18" s="1"/>
+      <c r="MS18" s="1"/>
+      <c r="MT18" s="1"/>
+      <c r="MU18" s="1"/>
+      <c r="MV18" s="1"/>
+      <c r="MW18" s="1"/>
+      <c r="MX18" s="1"/>
+      <c r="MY18" s="1"/>
+      <c r="MZ18" s="1"/>
+      <c r="NA18" s="1"/>
+      <c r="NB18" s="1"/>
+      <c r="NC18" s="1"/>
+      <c r="ND18" s="1"/>
+      <c r="NE18" s="1"/>
+      <c r="NF18" s="1"/>
+      <c r="NG18" s="1"/>
+      <c r="NH18" s="1"/>
+      <c r="NI18" s="1"/>
+      <c r="NJ18" s="1"/>
+      <c r="NK18" s="1"/>
+      <c r="NL18" s="1"/>
+      <c r="NM18" s="1"/>
+      <c r="NN18" s="1"/>
+      <c r="NO18" s="1"/>
+      <c r="NP18" s="1"/>
+      <c r="NQ18" s="1"/>
+      <c r="NR18" s="1"/>
+      <c r="NS18" s="1"/>
+      <c r="NT18" s="1"/>
+      <c r="NU18" s="1"/>
+      <c r="NV18" s="1"/>
+      <c r="NW18" s="1"/>
+      <c r="NX18" s="1"/>
+      <c r="NY18" s="1"/>
+      <c r="NZ18" s="1"/>
+      <c r="OA18" s="1"/>
+      <c r="OB18" s="1"/>
+      <c r="OC18" s="1"/>
+      <c r="OD18" s="1"/>
+      <c r="OE18" s="1"/>
+      <c r="OF18" s="1"/>
+      <c r="OG18" s="1"/>
+      <c r="OH18" s="1"/>
+      <c r="OI18" s="1"/>
+      <c r="OJ18" s="1"/>
+      <c r="OK18" s="1"/>
+      <c r="OL18" s="1"/>
+      <c r="OM18" s="1"/>
+      <c r="ON18" s="1"/>
+      <c r="OO18" s="1"/>
+      <c r="OP18" s="1"/>
+      <c r="OQ18" s="1"/>
+      <c r="OR18" s="1"/>
+      <c r="OS18" s="1"/>
+      <c r="OT18" s="1"/>
+      <c r="OU18" s="1"/>
+      <c r="OV18" s="1"/>
+      <c r="OW18" s="1"/>
+      <c r="OX18" s="1"/>
+      <c r="OY18" s="1"/>
+      <c r="OZ18" s="1"/>
+      <c r="PA18" s="1"/>
+      <c r="PB18" s="1"/>
+      <c r="PC18" s="1"/>
+      <c r="PD18" s="1"/>
+      <c r="PE18" s="1"/>
+      <c r="PF18" s="1"/>
+      <c r="PG18" s="1"/>
+      <c r="PH18" s="1"/>
+      <c r="PI18" s="1"/>
+      <c r="PJ18" s="1"/>
+      <c r="PK18" s="1"/>
+      <c r="PL18" s="1"/>
+      <c r="PM18" s="1"/>
+      <c r="PN18" s="1"/>
+      <c r="PO18" s="1"/>
+      <c r="PP18" s="1"/>
+      <c r="PQ18" s="1"/>
+      <c r="PR18" s="1"/>
+      <c r="PS18" s="1"/>
+      <c r="PT18" s="1"/>
+      <c r="PU18" s="1"/>
+      <c r="PV18" s="1"/>
+      <c r="PW18" s="1"/>
+      <c r="PX18" s="1"/>
+      <c r="PY18" s="1"/>
+      <c r="PZ18" s="1"/>
+      <c r="QA18" s="1"/>
+      <c r="QB18" s="1"/>
+      <c r="QC18" s="1"/>
+      <c r="QD18" s="1"/>
+      <c r="QE18" s="1"/>
+      <c r="QF18" s="1"/>
+      <c r="QG18" s="1"/>
+      <c r="QH18" s="1"/>
+      <c r="QI18" s="1"/>
+      <c r="QJ18" s="1"/>
+      <c r="QK18" s="1"/>
+      <c r="QL18" s="1"/>
+      <c r="QM18" s="1"/>
+      <c r="QN18" s="1"/>
+      <c r="QO18" s="1"/>
+      <c r="QP18" s="1"/>
+      <c r="QQ18" s="1"/>
+      <c r="QR18" s="1"/>
+      <c r="QS18" s="1"/>
+      <c r="QT18" s="1"/>
+      <c r="QU18" s="1"/>
+      <c r="QV18" s="1"/>
+      <c r="QW18" s="1"/>
+      <c r="QX18" s="1"/>
+      <c r="QY18" s="1"/>
+      <c r="QZ18" s="1"/>
+      <c r="RA18" s="1"/>
+      <c r="RB18" s="1"/>
+      <c r="RC18" s="1"/>
+      <c r="RD18" s="1"/>
+      <c r="RE18" s="1"/>
+      <c r="RF18" s="1"/>
+      <c r="RG18" s="1"/>
+      <c r="RH18" s="1"/>
+      <c r="RI18" s="1"/>
+      <c r="RJ18" s="1"/>
+      <c r="RK18" s="1"/>
+      <c r="RL18" s="1"/>
+      <c r="RM18" s="1"/>
+      <c r="RN18" s="1"/>
+      <c r="RO18" s="1"/>
+      <c r="RP18" s="1"/>
+      <c r="RQ18" s="1"/>
+      <c r="RR18" s="1"/>
+      <c r="RS18" s="1"/>
+      <c r="RT18" s="1"/>
+      <c r="RU18" s="1"/>
+      <c r="RV18" s="1"/>
+      <c r="RW18" s="1"/>
+      <c r="RX18" s="1"/>
+      <c r="RY18" s="1"/>
+      <c r="RZ18" s="1"/>
+      <c r="SA18" s="1"/>
+      <c r="SB18" s="1"/>
+      <c r="SC18" s="1"/>
+      <c r="SD18" s="1"/>
+      <c r="SE18" s="1"/>
+      <c r="SF18" s="1"/>
+      <c r="SG18" s="1"/>
+      <c r="SH18" s="1"/>
+      <c r="SI18" s="1"/>
+      <c r="SJ18" s="1"/>
+      <c r="SK18" s="1"/>
+      <c r="SL18" s="1"/>
+      <c r="SM18" s="1"/>
+      <c r="SN18" s="1"/>
+      <c r="SO18" s="1"/>
+      <c r="SP18" s="1"/>
+      <c r="SQ18" s="1"/>
+      <c r="SR18" s="1"/>
+      <c r="SS18" s="1"/>
+      <c r="ST18" s="1"/>
+      <c r="SU18" s="1"/>
+      <c r="SV18" s="1"/>
+      <c r="SW18" s="1"/>
+      <c r="SX18" s="1"/>
+      <c r="SY18" s="1"/>
+      <c r="SZ18" s="1"/>
+      <c r="TA18" s="1"/>
+      <c r="TB18" s="1"/>
+      <c r="TC18" s="1"/>
+      <c r="TD18" s="1"/>
+      <c r="TE18" s="1"/>
+      <c r="TF18" s="1"/>
+      <c r="TG18" s="1"/>
+      <c r="TH18" s="1"/>
+      <c r="TI18" s="1"/>
+      <c r="TJ18" s="1"/>
+      <c r="TK18" s="1"/>
+      <c r="TL18" s="1"/>
+      <c r="TM18" s="1"/>
+      <c r="TN18" s="1"/>
+      <c r="TO18" s="1"/>
+      <c r="TP18" s="1"/>
+      <c r="TQ18" s="1"/>
+      <c r="TR18" s="1"/>
+      <c r="TS18" s="1"/>
+      <c r="TT18" s="1"/>
+      <c r="TU18" s="1"/>
+      <c r="TV18" s="1"/>
+      <c r="TW18" s="1"/>
+      <c r="TX18" s="1"/>
+      <c r="TY18" s="1"/>
+      <c r="TZ18" s="1"/>
+    </row>
+    <row r="19" spans="1:546" ht="96.75" customHeight="1" thickBot="1">
+      <c r="A19" s="60" t="s">
+        <v>387</v>
+      </c>
+      <c r="B19" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E19" s="62">
+        <v>46277</v>
+      </c>
+      <c r="F19" s="62">
+        <v>46338</v>
+      </c>
+      <c r="G19" s="62">
+        <v>46089</v>
+      </c>
+      <c r="H19" s="61" t="s">
+        <v>211</v>
+      </c>
+      <c r="I19" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="J19" s="61" t="s">
+        <v>213</v>
+      </c>
+      <c r="K19" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="L19" s="61" t="s">
+        <v>214</v>
+      </c>
+      <c r="M19" s="64" t="s">
+        <v>215</v>
+      </c>
+      <c r="N19" s="75" t="s">
+        <v>158</v>
+      </c>
+      <c r="O19" s="75" t="s">
+        <v>228</v>
+      </c>
+      <c r="P19" s="75" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q19" s="79" t="s">
+        <v>330</v>
+      </c>
+      <c r="R19" s="67" t="s">
+        <v>331</v>
+      </c>
+      <c r="S19" s="67" t="s">
+        <v>332</v>
+      </c>
+      <c r="T19" s="67" t="s">
+        <v>333</v>
+      </c>
+      <c r="U19" s="67" t="s">
+        <v>334</v>
+      </c>
+      <c r="V19" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W19" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="X19" s="67" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="20" spans="1:546" ht="86.25" customHeight="1" thickBot="1">
+      <c r="A20" s="66" t="s">
+        <v>216</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>217</v>
+      </c>
+      <c r="C20" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="69">
+        <v>2026</v>
+      </c>
+      <c r="E20" s="70">
+        <v>46062</v>
+      </c>
+      <c r="F20" s="70">
+        <v>46121</v>
+      </c>
+      <c r="G20" s="70">
+        <v>46146</v>
+      </c>
+      <c r="H20" s="69" t="s">
+        <v>219</v>
+      </c>
+      <c r="I20" s="69" t="s">
+        <v>220</v>
+      </c>
+      <c r="J20" s="69" t="s">
+        <v>221</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="M20" s="71" t="s">
+        <v>222</v>
+      </c>
+      <c r="N20" s="76" t="s">
+        <v>112</v>
+      </c>
+      <c r="O20" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="P20" s="76" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q20" s="79" t="s">
+        <v>335</v>
+      </c>
+      <c r="R20" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="S20" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="T20" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="U20" s="67" t="s">
+        <v>339</v>
+      </c>
+      <c r="V20" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W20" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="X20" s="67" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:546" ht="141.75" customHeight="1" thickBot="1">
+      <c r="A21" s="72" t="s">
+        <v>386</v>
+      </c>
+      <c r="B21" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>224</v>
+      </c>
+      <c r="D21" s="68">
+        <v>2026</v>
+      </c>
+      <c r="E21" s="73">
+        <v>46153</v>
+      </c>
+      <c r="F21" s="73">
+        <v>46184</v>
+      </c>
+      <c r="G21" s="68" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>225</v>
+      </c>
+      <c r="I21" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="J21" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="68" t="s">
+        <v>227</v>
+      </c>
+      <c r="M21" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="N21" s="77" t="s">
+        <v>232</v>
+      </c>
+      <c r="O21" s="77" t="s">
+        <v>233</v>
+      </c>
+      <c r="P21" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q21" s="79" t="s">
+        <v>340</v>
+      </c>
+      <c r="R21" s="67" t="s">
+        <v>341</v>
+      </c>
+      <c r="S21" s="82" t="s">
+        <v>342</v>
+      </c>
+      <c r="T21" s="82" t="s">
+        <v>343</v>
+      </c>
+      <c r="U21" s="82" t="s">
+        <v>344</v>
+      </c>
+      <c r="V21" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W21" s="67" t="s">
+        <v>248</v>
+      </c>
+      <c r="X21" s="67" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="22" spans="1:546" ht="117.75" customHeight="1" thickBot="1">
+      <c r="A22" s="83" t="s">
+        <v>385</v>
+      </c>
+      <c r="B22" s="65" t="s">
+        <v>345</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E22" s="62">
+        <v>46181</v>
+      </c>
+      <c r="F22" s="62">
+        <v>46211</v>
+      </c>
+      <c r="G22" s="63">
+        <v>46145</v>
+      </c>
+      <c r="H22" s="61" t="s">
+        <v>347</v>
+      </c>
+      <c r="I22" s="61" t="s">
+        <v>348</v>
+      </c>
+      <c r="J22" s="61" t="s">
+        <v>349</v>
+      </c>
+      <c r="K22" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="61" t="s">
+        <v>227</v>
+      </c>
+      <c r="M22" s="64" t="s">
+        <v>350</v>
+      </c>
+      <c r="N22" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="O22" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="P22" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q22" s="84" t="s">
+        <v>340</v>
+      </c>
+      <c r="R22" s="65" t="s">
+        <v>352</v>
+      </c>
+      <c r="S22" s="85" t="s">
+        <v>353</v>
+      </c>
+      <c r="T22" s="85" t="s">
+        <v>354</v>
+      </c>
+      <c r="U22" s="65" t="s">
+        <v>355</v>
+      </c>
+      <c r="V22" s="61" t="s">
+        <v>252</v>
+      </c>
+      <c r="W22" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="X22" s="65" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:546" ht="108" customHeight="1" thickBot="1">
+      <c r="A23" s="86" t="s">
+        <v>384</v>
+      </c>
+      <c r="B23" s="65" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>357</v>
+      </c>
+      <c r="D23" s="61">
+        <v>2026</v>
+      </c>
+      <c r="E23" s="62">
+        <v>46274</v>
+      </c>
+      <c r="F23" s="62">
+        <v>46335</v>
+      </c>
+      <c r="G23" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="87" t="s">
+        <v>358</v>
+      </c>
+      <c r="I23" s="61" t="s">
+        <v>359</v>
+      </c>
+      <c r="J23" s="61" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="L23" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="M23" s="64" t="s">
+        <v>360</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q23" s="84" t="s">
+        <v>369</v>
+      </c>
+      <c r="R23" s="65" t="s">
+        <v>370</v>
+      </c>
+      <c r="S23" s="65" t="s">
+        <v>371</v>
+      </c>
+      <c r="T23" s="65" t="s">
+        <v>372</v>
+      </c>
+      <c r="U23" s="65" t="s">
+        <v>373</v>
+      </c>
+      <c r="V23" s="61" t="s">
+        <v>252</v>
+      </c>
+      <c r="W23" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="X23" s="65" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:546" ht="89.25" customHeight="1" thickBot="1">
+      <c r="A24" s="88" t="s">
+        <v>383</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>361</v>
+      </c>
+      <c r="C24" s="68" t="s">
+        <v>362</v>
+      </c>
+      <c r="D24" s="68">
+        <v>2026</v>
+      </c>
+      <c r="E24" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="F24" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="G24" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>366</v>
+      </c>
+      <c r="I24" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J24" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="M2" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="N2" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="O2" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="P2" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q2" s="80" t="s">
-        <v>246</v>
-      </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="69" t="s">
-        <v>247</v>
-      </c>
-      <c r="T2" s="69" t="s">
+      <c r="K24" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="L24" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="M24" s="71" t="s">
+        <v>368</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q24" s="89" t="s">
+        <v>374</v>
+      </c>
+      <c r="R24" s="67" t="s">
+        <v>375</v>
+      </c>
+      <c r="S24" s="67" t="s">
+        <v>376</v>
+      </c>
+      <c r="T24" s="67" t="s">
+        <v>377</v>
+      </c>
+      <c r="U24" s="67" t="s">
+        <v>378</v>
+      </c>
+      <c r="V24" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="W24" s="67" t="s">
         <v>248</v>
       </c>
-      <c r="U2" s="69" t="s">
-        <v>249</v>
-      </c>
-      <c r="V2" s="69" t="s">
-        <v>250</v>
-      </c>
-      <c r="W2" s="82" t="s">
-        <v>251</v>
-      </c>
-      <c r="X2" s="69" t="s">
-        <v>252</v>
+      <c r="X24" s="67" t="s">
+        <v>329</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="11" customFormat="1" ht="94.5" customHeight="1" thickBot="1">
-      <c r="A3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="16">
-        <v>2026</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="M3" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="O3" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="P3" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q3" s="80" t="s">
-        <v>253</v>
-      </c>
-      <c r="R3" s="81"/>
-      <c r="S3" s="69" t="s">
-        <v>254</v>
-      </c>
-      <c r="T3" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="U3" s="69" t="s">
-        <v>256</v>
-      </c>
-      <c r="V3" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W3" s="82" t="s">
-        <v>251</v>
-      </c>
-      <c r="X3" s="69" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" s="11" customFormat="1" ht="120" customHeight="1" thickBot="1">
-      <c r="A4" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="16">
-        <v>2026</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="M4" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="O4" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="P4" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q4" s="80" t="s">
-        <v>257</v>
-      </c>
-      <c r="R4" s="69" t="s">
-        <v>258</v>
-      </c>
-      <c r="S4" s="69" t="s">
-        <v>259</v>
-      </c>
-      <c r="T4" s="69" t="s">
-        <v>260</v>
-      </c>
-      <c r="U4" s="69" t="s">
-        <v>261</v>
-      </c>
-      <c r="V4" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W4" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="X4" s="69" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" s="11" customFormat="1" ht="127.5" customHeight="1" thickBot="1">
-      <c r="A5" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="18">
-        <v>2026</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="P5" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q5" s="80" t="s">
-        <v>262</v>
-      </c>
-      <c r="R5" s="69" t="s">
-        <v>263</v>
-      </c>
-      <c r="S5" s="69" t="s">
-        <v>264</v>
-      </c>
-      <c r="T5" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="U5" s="69" t="s">
-        <v>265</v>
-      </c>
-      <c r="V5" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W5" s="81"/>
-      <c r="X5" s="69" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" s="11" customFormat="1" ht="120" customHeight="1" thickBot="1">
-      <c r="A6" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="18">
-        <v>2026</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K6" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="M6" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="N6" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="O6" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="P6" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q6" s="80" t="s">
-        <v>266</v>
-      </c>
-      <c r="R6" s="69" t="s">
-        <v>267</v>
-      </c>
-      <c r="S6" s="69" t="s">
-        <v>268</v>
-      </c>
-      <c r="T6" s="69" t="s">
-        <v>269</v>
-      </c>
-      <c r="U6" s="69" t="s">
-        <v>270</v>
-      </c>
-      <c r="V6" s="68" t="s">
-        <v>255</v>
-      </c>
-      <c r="W6" s="68" t="s">
-        <v>271</v>
-      </c>
-      <c r="X6" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" s="11" customFormat="1" ht="114" customHeight="1" thickBot="1">
-      <c r="A7" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="18">
-        <v>2026</v>
-      </c>
-      <c r="E7" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="K7" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="N7" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="O7" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P7" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q7" s="80" t="s">
-        <v>272</v>
-      </c>
-      <c r="R7" s="69" t="s">
-        <v>273</v>
-      </c>
-      <c r="S7" s="69" t="s">
-        <v>274</v>
-      </c>
-      <c r="T7" s="69" t="s">
-        <v>275</v>
-      </c>
-      <c r="U7" s="69" t="s">
-        <v>276</v>
-      </c>
-      <c r="V7" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W7" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="X7" s="69" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" s="11" customFormat="1" ht="132" customHeight="1" thickBot="1">
-      <c r="A8" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="21">
-        <v>2026</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="M8" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="N8" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="O8" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="P8" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q8" s="80" t="s">
-        <v>277</v>
-      </c>
-      <c r="R8" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="S8" s="69" t="s">
-        <v>279</v>
-      </c>
-      <c r="T8" s="69" t="s">
-        <v>280</v>
-      </c>
-      <c r="U8" s="69" t="s">
-        <v>281</v>
-      </c>
-      <c r="V8" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W8" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="X8" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" s="15" customFormat="1" ht="105.75" customHeight="1" thickBot="1">
-      <c r="A9" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="21">
-        <v>2026</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="M9" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="O9" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="P9" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q9" s="80" t="s">
-        <v>282</v>
-      </c>
-      <c r="R9" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="S9" s="69" t="s">
-        <v>283</v>
-      </c>
-      <c r="T9" s="69" t="s">
-        <v>284</v>
-      </c>
-      <c r="U9" s="69" t="s">
-        <v>285</v>
-      </c>
-      <c r="V9" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W9" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="X9" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="95.25" customHeight="1" thickBot="1">
-      <c r="A10" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="21">
-        <v>2026</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="25">
-        <v>46026</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="M10" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="N10" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="O10" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="P10" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q10" s="80" t="s">
-        <v>286</v>
-      </c>
-      <c r="R10" s="69" t="s">
-        <v>278</v>
-      </c>
-      <c r="S10" s="69" t="s">
-        <v>287</v>
-      </c>
-      <c r="T10" s="69" t="s">
-        <v>288</v>
-      </c>
-      <c r="U10" s="69" t="s">
-        <v>289</v>
-      </c>
-      <c r="V10" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W10" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="X10" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" ht="108" customHeight="1" thickBot="1">
-      <c r="A11" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="29">
-        <v>2026</v>
-      </c>
-      <c r="E11" s="42">
-        <v>46331</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="G11" s="30">
-        <v>46175</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="M11" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="N11" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="O11" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="P11" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q11" s="80" t="s">
-        <v>290</v>
-      </c>
-      <c r="R11" s="69" t="s">
-        <v>291</v>
-      </c>
-      <c r="S11" s="69" t="s">
-        <v>292</v>
-      </c>
-      <c r="T11" s="69" t="s">
-        <v>293</v>
-      </c>
-      <c r="U11" s="69" t="s">
-        <v>294</v>
-      </c>
-      <c r="V11" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W11" s="69" t="s">
-        <v>295</v>
-      </c>
-      <c r="X11" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" ht="156" customHeight="1" thickBot="1">
-      <c r="A12" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="33">
-        <v>2026</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="G12" s="34">
-        <v>46240</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="I12" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="J12" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="K12" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="L12" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="M12" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="N12" s="37" t="s">
-        <v>159</v>
-      </c>
-      <c r="O12" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="P12" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q12" s="80" t="s">
-        <v>296</v>
-      </c>
-      <c r="R12" s="69" t="s">
-        <v>297</v>
-      </c>
-      <c r="S12" s="69" t="s">
-        <v>298</v>
-      </c>
-      <c r="T12" s="69" t="s">
-        <v>299</v>
-      </c>
-      <c r="U12" s="69" t="s">
-        <v>300</v>
-      </c>
-      <c r="V12" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W12" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="X12" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="159.75" customHeight="1" thickBot="1">
-      <c r="A13" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="33">
-        <v>2026</v>
-      </c>
-      <c r="E13" s="34">
-        <v>46210</v>
-      </c>
-      <c r="F13" s="34">
-        <v>46272</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="I13" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="J13" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="M13" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="O13" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="P13" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q13" s="80" t="s">
-        <v>301</v>
-      </c>
-      <c r="R13" s="69" t="s">
-        <v>302</v>
-      </c>
-      <c r="S13" s="69" t="s">
-        <v>303</v>
-      </c>
-      <c r="T13" s="69" t="s">
-        <v>304</v>
-      </c>
-      <c r="U13" s="69" t="s">
-        <v>305</v>
-      </c>
-      <c r="V13" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W13" s="69" t="s">
-        <v>306</v>
-      </c>
-      <c r="X13" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="135.75" customHeight="1" thickBot="1">
-      <c r="A14" s="32" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="33">
-        <v>2026</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="34">
-        <v>46063</v>
-      </c>
-      <c r="G14" s="34">
-        <v>46030</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="I14" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="J14" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="K14" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="L14" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="M14" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="N14" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="O14" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="P14" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q14" s="80" t="s">
-        <v>307</v>
-      </c>
-      <c r="R14" s="69" t="s">
-        <v>308</v>
-      </c>
-      <c r="S14" s="69" t="s">
-        <v>309</v>
-      </c>
-      <c r="T14" s="69" t="s">
-        <v>310</v>
-      </c>
-      <c r="U14" s="69" t="s">
-        <v>311</v>
-      </c>
-      <c r="V14" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W14" s="69" t="s">
-        <v>251</v>
-      </c>
-      <c r="X14" s="69" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="150.75" customHeight="1" thickBot="1">
-      <c r="A15" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="D15" s="43">
-        <v>2026</v>
-      </c>
-      <c r="E15" s="45">
-        <v>46092</v>
-      </c>
-      <c r="F15" s="45">
-        <v>46153</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="H15" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="I15" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="J15" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="L15" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="M15" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="N15" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="O15" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="P15" s="47" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q15" s="80" t="s">
-        <v>312</v>
-      </c>
-      <c r="R15" s="69" t="s">
-        <v>313</v>
-      </c>
-      <c r="S15" s="69" t="s">
-        <v>314</v>
-      </c>
-      <c r="T15" s="69" t="s">
-        <v>315</v>
-      </c>
-      <c r="U15" s="69" t="s">
-        <v>316</v>
-      </c>
-      <c r="V15" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W15" s="69" t="s">
-        <v>317</v>
-      </c>
-      <c r="X15" s="69" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" s="48" customFormat="1" ht="87" customHeight="1" thickBot="1">
-      <c r="A16" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="C16" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="D16" s="51">
-        <v>2026</v>
-      </c>
-      <c r="E16" s="52">
-        <v>46090</v>
-      </c>
-      <c r="F16" s="52">
-        <v>46121</v>
-      </c>
-      <c r="G16" s="52">
-        <v>46115</v>
-      </c>
-      <c r="H16" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="I16" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="J16" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="M16" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="N16" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="O16" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="P16" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q16" s="80" t="s">
-        <v>318</v>
-      </c>
-      <c r="R16" s="69" t="s">
-        <v>319</v>
-      </c>
-      <c r="S16" s="69" t="s">
-        <v>320</v>
-      </c>
-      <c r="T16" s="68" t="s">
-        <v>321</v>
-      </c>
-      <c r="U16" s="68" t="s">
-        <v>322</v>
-      </c>
-      <c r="V16" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W16" s="68" t="s">
-        <v>251</v>
-      </c>
-      <c r="X16" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" s="48" customFormat="1" ht="92.25" customHeight="1" thickBot="1">
-      <c r="A17" s="54" t="s">
-        <v>180</v>
-      </c>
-      <c r="B17" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="D17" s="56">
-        <v>2026</v>
-      </c>
-      <c r="E17" s="56" t="s">
-        <v>183</v>
-      </c>
-      <c r="F17" s="56" t="s">
-        <v>184</v>
-      </c>
-      <c r="G17" s="57">
-        <v>46084</v>
-      </c>
-      <c r="H17" s="56" t="s">
-        <v>185</v>
-      </c>
-      <c r="I17" s="56" t="s">
-        <v>186</v>
-      </c>
-      <c r="J17" s="56" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="55" t="s">
-        <v>105</v>
-      </c>
-      <c r="M17" s="58" t="s">
-        <v>187</v>
-      </c>
-      <c r="N17" s="60" t="s">
-        <v>112</v>
-      </c>
-      <c r="O17" s="60" t="s">
-        <v>190</v>
-      </c>
-      <c r="P17" s="60" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q17" s="80" t="s">
-        <v>277</v>
-      </c>
-      <c r="R17" s="69" t="s">
-        <v>323</v>
-      </c>
-      <c r="S17" s="69" t="s">
-        <v>324</v>
-      </c>
-      <c r="T17" s="69" t="s">
-        <v>325</v>
-      </c>
-      <c r="U17" s="69" t="s">
-        <v>326</v>
-      </c>
-      <c r="V17" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W17" s="68" t="s">
-        <v>251</v>
-      </c>
-      <c r="X17" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" s="48" customFormat="1" ht="90" customHeight="1" thickBot="1">
-      <c r="A18" s="61" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" s="62" t="s">
-        <v>202</v>
-      </c>
-      <c r="D18" s="62">
-        <v>2026</v>
-      </c>
-      <c r="E18" s="63">
-        <v>46212</v>
-      </c>
-      <c r="F18" s="63">
-        <v>46333</v>
-      </c>
-      <c r="G18" s="64" t="s">
-        <v>209</v>
-      </c>
-      <c r="H18" s="62" t="s">
-        <v>203</v>
-      </c>
-      <c r="I18" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="K18" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="62" t="s">
-        <v>205</v>
-      </c>
-      <c r="M18" s="65" t="s">
-        <v>206</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="O18" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="P18" s="36" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q18" s="80" t="s">
-        <v>327</v>
-      </c>
-      <c r="R18" s="69" t="s">
-        <v>328</v>
-      </c>
-      <c r="S18" s="69" t="s">
-        <v>329</v>
-      </c>
-      <c r="T18" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="U18" s="69" t="s">
-        <v>330</v>
-      </c>
-      <c r="V18" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W18" s="68" t="s">
-        <v>331</v>
-      </c>
-      <c r="X18" s="68" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" ht="96.75" customHeight="1" thickBot="1">
-      <c r="A19" s="61" t="s">
-        <v>210</v>
-      </c>
-      <c r="B19" s="66" t="s">
-        <v>211</v>
-      </c>
-      <c r="C19" s="62" t="s">
-        <v>212</v>
-      </c>
-      <c r="D19" s="62">
-        <v>2026</v>
-      </c>
-      <c r="E19" s="63">
-        <v>46277</v>
-      </c>
-      <c r="F19" s="63">
-        <v>46338</v>
-      </c>
-      <c r="G19" s="63">
-        <v>46089</v>
-      </c>
-      <c r="H19" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="I19" s="62" t="s">
-        <v>214</v>
-      </c>
-      <c r="J19" s="62" t="s">
-        <v>215</v>
-      </c>
-      <c r="K19" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="62" t="s">
-        <v>216</v>
-      </c>
-      <c r="M19" s="65" t="s">
-        <v>217</v>
-      </c>
-      <c r="N19" s="76" t="s">
-        <v>159</v>
-      </c>
-      <c r="O19" s="76" t="s">
-        <v>231</v>
-      </c>
-      <c r="P19" s="76" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q19" s="80" t="s">
-        <v>333</v>
-      </c>
-      <c r="R19" s="68" t="s">
-        <v>334</v>
-      </c>
-      <c r="S19" s="68" t="s">
-        <v>335</v>
-      </c>
-      <c r="T19" s="68" t="s">
-        <v>336</v>
-      </c>
-      <c r="U19" s="68" t="s">
-        <v>337</v>
-      </c>
-      <c r="V19" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W19" s="68" t="s">
-        <v>251</v>
-      </c>
-      <c r="X19" s="68" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" ht="86.25" customHeight="1" thickBot="1">
-      <c r="A20" s="67" t="s">
-        <v>218</v>
-      </c>
-      <c r="B20" s="68" t="s">
-        <v>219</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>220</v>
-      </c>
-      <c r="D20" s="70">
-        <v>2026</v>
-      </c>
-      <c r="E20" s="71">
-        <v>46062</v>
-      </c>
-      <c r="F20" s="71">
-        <v>46121</v>
-      </c>
-      <c r="G20" s="71">
-        <v>46146</v>
-      </c>
-      <c r="H20" s="70" t="s">
-        <v>221</v>
-      </c>
-      <c r="I20" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="J20" s="70" t="s">
-        <v>223</v>
-      </c>
-      <c r="K20" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="69" t="s">
-        <v>230</v>
-      </c>
-      <c r="M20" s="72" t="s">
-        <v>224</v>
-      </c>
-      <c r="N20" s="77" t="s">
-        <v>112</v>
-      </c>
-      <c r="O20" s="77" t="s">
-        <v>233</v>
-      </c>
-      <c r="P20" s="77" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q20" s="80" t="s">
-        <v>338</v>
-      </c>
-      <c r="R20" s="68" t="s">
-        <v>339</v>
-      </c>
-      <c r="S20" s="68" t="s">
-        <v>340</v>
-      </c>
-      <c r="T20" s="68" t="s">
-        <v>341</v>
-      </c>
-      <c r="U20" s="68" t="s">
-        <v>342</v>
-      </c>
-      <c r="V20" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W20" s="68" t="s">
-        <v>251</v>
-      </c>
-      <c r="X20" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" ht="141.75" customHeight="1" thickBot="1">
-      <c r="A21" s="73" t="s">
-        <v>225</v>
-      </c>
-      <c r="B21" s="68" t="s">
-        <v>226</v>
-      </c>
-      <c r="C21" s="69" t="s">
-        <v>227</v>
-      </c>
-      <c r="D21" s="69">
-        <v>2026</v>
-      </c>
-      <c r="E21" s="74">
-        <v>46153</v>
-      </c>
-      <c r="F21" s="74">
-        <v>46184</v>
-      </c>
-      <c r="G21" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="H21" s="69" t="s">
-        <v>228</v>
-      </c>
-      <c r="I21" s="69" t="s">
-        <v>186</v>
-      </c>
-      <c r="J21" s="69" t="s">
-        <v>41</v>
-      </c>
-      <c r="K21" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="69" t="s">
-        <v>230</v>
-      </c>
-      <c r="M21" s="75" t="s">
-        <v>229</v>
-      </c>
-      <c r="N21" s="78" t="s">
-        <v>235</v>
-      </c>
-      <c r="O21" s="78" t="s">
-        <v>236</v>
-      </c>
-      <c r="P21" s="78" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q21" s="80" t="s">
-        <v>343</v>
-      </c>
-      <c r="R21" s="68" t="s">
-        <v>344</v>
-      </c>
-      <c r="S21" s="83" t="s">
-        <v>345</v>
-      </c>
-      <c r="T21" s="83" t="s">
-        <v>346</v>
-      </c>
-      <c r="U21" s="83" t="s">
-        <v>347</v>
-      </c>
-      <c r="V21" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="W21" s="68" t="s">
-        <v>251</v>
-      </c>
-      <c r="X21" s="68" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" ht="117.75" customHeight="1" thickBot="1">
-      <c r="A22" s="84" t="s">
-        <v>348</v>
-      </c>
-      <c r="B22" s="66" t="s">
-        <v>349</v>
-      </c>
-      <c r="C22" s="62" t="s">
-        <v>350</v>
-      </c>
-      <c r="D22" s="62">
-        <v>2026</v>
-      </c>
-      <c r="E22" s="63">
-        <v>46181</v>
-      </c>
-      <c r="F22" s="63">
-        <v>46211</v>
-      </c>
-      <c r="G22" s="64">
-        <v>46145</v>
-      </c>
-      <c r="H22" s="62" t="s">
-        <v>351</v>
-      </c>
-      <c r="I22" s="62" t="s">
-        <v>352</v>
-      </c>
-      <c r="J22" s="62" t="s">
-        <v>353</v>
-      </c>
-      <c r="K22" s="62" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="M22" s="65" t="s">
-        <v>354</v>
-      </c>
-      <c r="N22" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="O22" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="P22" s="36" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q22" s="85" t="s">
-        <v>343</v>
-      </c>
-      <c r="R22" s="66" t="s">
-        <v>356</v>
-      </c>
-      <c r="S22" s="86" t="s">
-        <v>357</v>
-      </c>
-      <c r="T22" s="86" t="s">
-        <v>358</v>
-      </c>
-      <c r="U22" s="66" t="s">
-        <v>359</v>
-      </c>
-      <c r="V22" s="62" t="s">
-        <v>255</v>
-      </c>
-      <c r="W22" s="66" t="s">
-        <v>251</v>
-      </c>
-      <c r="X22" s="66" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" ht="15.75" thickBot="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="9"/>
-    </row>
-    <row r="24" spans="1:24" ht="15.75" thickBot="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="9"/>
-    </row>
-    <row r="25" spans="1:24" ht="15.75" thickBot="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="4"/>
+    <row r="25" spans="1:546" ht="15.75" thickBot="1">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="9"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4111,8 +5961,10 @@
     <hyperlink ref="M20" r:id="rId12" xr:uid="{8764E6FA-24BB-4CD3-B7F0-A477686AF5B7}"/>
     <hyperlink ref="M21" r:id="rId13" xr:uid="{9E69CB45-2D00-482D-B3EC-C054EF664AFF}"/>
     <hyperlink ref="M22" r:id="rId14" xr:uid="{5CCA6143-A9EC-4CB6-B3D2-4F8671964932}"/>
+    <hyperlink ref="M23" r:id="rId15" display="https://controlo2026.apca.pt/" xr:uid="{9244AD77-C37F-4E45-9C8A-6361A2809806}"/>
+    <hyperlink ref="M24" r:id="rId16" display="https://icacit.org.pe/symposium" xr:uid="{77A93079-513E-498C-8316-3E4DC98BB598}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId17"/>
 </worksheet>
 </file>